--- a/examples/example2/Example2.xlsx
+++ b/examples/example2/Example2.xlsx
@@ -6,20 +6,21 @@
     <sheet state="visible" name="SDTM AE" sheetId="1" r:id="rId4"/>
     <sheet state="visible" name="SDTM LB" sheetId="2" r:id="rId5"/>
     <sheet state="visible" name="Source LabResults" sheetId="3" r:id="rId6"/>
-    <sheet state="visible" name="RWDLineage-Table" sheetId="4" r:id="rId7"/>
+    <sheet state="visible" name="RWDLineageFull-Table" sheetId="4" r:id="rId7"/>
+    <sheet state="visible" name="RWDLineageAEtoSource-Table" sheetId="5" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="BDp/rI5/PuDwbD3TWKuX+4D2lRAotYGxw3zHItcEQZE="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataChecksum="4LWpCG6rA7Wf9jdQC/J2kTZGJkWgbD7X/U3cwDur9zs="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1121" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1279" uniqueCount="170">
   <si>
     <t>USUBJID</t>
   </si>
@@ -222,13 +223,10 @@
     <t>Filesystem</t>
   </si>
   <si>
-    <t>Tabuar</t>
+    <t>Tabular</t>
   </si>
   <si>
     <t>https://github.com/cdisc-org/DataExchange-RWD-Lineage/blob/main/examples/example2/data/sdtm/LB.csv</t>
-  </si>
-  <si>
-    <t>Tabular</t>
   </si>
   <si>
     <t>https://github.com/cdisc-org/DataExchange-RWD-Lineage/blob/main/examples/example2/data/source/LabResults.csv</t>
@@ -538,7 +536,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="13">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="12">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -600,13 +601,8 @@
       <color theme="1"/>
       <name val="Arial"/>
     </font>
-    <font>
-      <u/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -615,14 +611,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor theme="9"/>
+        <fgColor rgb="FFC9DAF8"/>
+        <bgColor rgb="FFC9DAF8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor theme="8"/>
+        <fgColor rgb="FFFCE5CD"/>
+        <bgColor rgb="FFFCE5CD"/>
       </patternFill>
     </fill>
     <fill>
@@ -639,8 +635,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF6D01"/>
-        <bgColor rgb="FFFF6D01"/>
+        <fgColor rgb="FFA4C2F4"/>
+        <bgColor rgb="FFA4C2F4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9CB9C"/>
+        <bgColor rgb="FFF9CB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -650,7 +652,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="58">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -665,8 +667,8 @@
     </xf>
     <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="3" fontId="2" numFmtId="14" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
@@ -678,8 +680,8 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="14" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
@@ -705,8 +707,14 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="14" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="14" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -727,12 +735,18 @@
     <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
@@ -743,6 +757,9 @@
     <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
@@ -750,25 +767,29 @@
     <xf borderId="0" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="14" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="14" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="3" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="6" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="6" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="6" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="6" fontId="3" numFmtId="14" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" vertical="bottom"/>
+    <xf borderId="0" fillId="3" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
@@ -776,6 +797,17 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="2" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="6" fontId="3" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="7" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="7" fontId="3" numFmtId="14" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="7" fontId="3" numFmtId="14" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -798,6 +830,10 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -9152,7 +9188,7 @@
         <v>25</v>
       </c>
       <c r="E2" s="11">
-        <v>45332.0</v>
+        <v>45698.0</v>
       </c>
       <c r="F2" s="12">
         <f t="shared" ref="F2:F13" si="1">H2*0.0167</f>
@@ -9205,7 +9241,7 @@
         <v>30</v>
       </c>
       <c r="E3" s="11">
-        <v>45332.0</v>
+        <v>45698.0</v>
       </c>
       <c r="F3" s="12">
         <f t="shared" si="1"/>
@@ -9258,7 +9294,7 @@
         <v>32</v>
       </c>
       <c r="E4" s="11">
-        <v>45332.0</v>
+        <v>45698.0</v>
       </c>
       <c r="F4" s="12">
         <f t="shared" si="1"/>
@@ -9791,7 +9827,7 @@
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="18"/>
-      <c r="E15" s="3"/>
+      <c r="E15" s="11"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
@@ -9803,7 +9839,7 @@
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="18"/>
-      <c r="E16" s="3"/>
+      <c r="E16" s="11"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
@@ -21664,13 +21700,13 @@
       <c r="C2" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="20">
         <v>45332.0</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="20"/>
+      <c r="F2" s="21"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="19" t="s">
@@ -21682,13 +21718,13 @@
       <c r="C3" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="20">
         <v>45332.0</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F3" s="20"/>
+      <c r="F3" s="21"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="19" t="s">
@@ -21700,13 +21736,13 @@
       <c r="C4" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="20">
         <v>45332.0</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="F4" s="20"/>
+      <c r="F4" s="21"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="19" t="s">
@@ -21718,13 +21754,13 @@
       <c r="C5" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="20">
         <v>45741.0</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F5" s="20"/>
+      <c r="F5" s="21"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="19" t="s">
@@ -21733,16 +21769,16 @@
       <c r="B6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="20">
         <v>45741.0</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F6" s="20"/>
+      <c r="F6" s="21"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="19" t="s">
@@ -21751,16 +21787,16 @@
       <c r="B7" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="20">
         <v>45741.0</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="F7" s="20"/>
+      <c r="F7" s="21"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="19" t="s">
@@ -21772,13 +21808,13 @@
       <c r="C8" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="20">
         <v>45590.0</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F8" s="20"/>
+      <c r="F8" s="21"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="19" t="s">
@@ -21790,13 +21826,13 @@
       <c r="C9" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="20">
         <v>45590.0</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="F9" s="20"/>
+      <c r="F9" s="21"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="19" t="s">
@@ -21808,13 +21844,13 @@
       <c r="C10" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="20">
         <v>45590.0</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F10" s="20"/>
+      <c r="F10" s="21"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="19" t="s">
@@ -21826,13 +21862,13 @@
       <c r="C11" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="23">
         <v>45967.0</v>
       </c>
       <c r="E11" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="F11" s="20"/>
+      <c r="F11" s="21"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="19" t="s">
@@ -21844,13 +21880,13 @@
       <c r="C12" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="23">
         <v>45967.0</v>
       </c>
       <c r="E12" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="F12" s="20"/>
+      <c r="F12" s="21"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="19" t="s">
@@ -21862,13 +21898,13 @@
       <c r="C13" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="23">
         <v>45967.0</v>
       </c>
       <c r="E13" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="F13" s="20"/>
+      <c r="F13" s="21"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="9"/>
@@ -28794,3829 +28830,3829 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="20.13"/>
+    <col customWidth="1" min="1" max="1" width="10.5"/>
     <col customWidth="1" min="12" max="12" width="11.13"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="22"/>
-      <c r="B1" s="23" t="s">
+      <c r="A1" s="24"/>
+      <c r="B1" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="G1" s="26" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="D2" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="E2" s="25" t="s">
+      <c r="E2" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="F2" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="G2" s="26" t="s">
+      <c r="G2" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="H2" s="26" t="s">
+      <c r="H2" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="I2" s="26" t="s">
+      <c r="I2" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="J2" s="26" t="s">
+      <c r="J2" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="K2" s="26" t="s">
+      <c r="K2" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="L2" s="26" t="s">
+      <c r="L2" s="28" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="D3" s="28" t="s">
+      <c r="D3" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="E3" s="29">
+      <c r="E3" s="32">
         <v>10.0</v>
       </c>
-      <c r="F3" s="29" t="s">
+      <c r="F3" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="29" t="s">
+      <c r="G3" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="H3" s="29" t="s">
+      <c r="H3" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="I3" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="I3" s="30" t="s">
+      <c r="J3" s="32">
+        <v>10.0</v>
+      </c>
+      <c r="K3" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="L3" s="32" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="J3" s="29">
+      <c r="B4" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="D4" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="E4" s="32">
+        <v>11.0</v>
+      </c>
+      <c r="F4" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="H4" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="I4" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="J4" s="32">
+        <v>11.0</v>
+      </c>
+      <c r="K4" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" s="32" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="E5" s="32">
+        <v>12.0</v>
+      </c>
+      <c r="F5" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="H5" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="I5" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="J5" s="32">
+        <v>12.0</v>
+      </c>
+      <c r="K5" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="L5" s="32" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D6" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E6" s="21">
+        <v>1.0</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H6" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I6" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="J6" s="21">
+        <v>1.0</v>
+      </c>
+      <c r="K6" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="L6" s="21" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="21">
+        <v>2.0</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H7" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I7" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="J7" s="21">
+        <v>2.0</v>
+      </c>
+      <c r="K7" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="L7" s="21" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E8" s="21">
+        <v>3.0</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H8" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I8" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="J8" s="21">
+        <v>3.0</v>
+      </c>
+      <c r="K8" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="L8" s="21" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E9" s="21">
+        <v>4.0</v>
+      </c>
+      <c r="F9" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H9" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I9" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="J9" s="21">
+        <v>4.0</v>
+      </c>
+      <c r="K9" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="L9" s="21" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E10" s="21">
+        <v>5.0</v>
+      </c>
+      <c r="F10" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I10" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="J10" s="21">
+        <v>5.0</v>
+      </c>
+      <c r="K10" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="L10" s="21" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E11" s="21">
+        <v>6.0</v>
+      </c>
+      <c r="F11" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I11" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="J11" s="21">
+        <v>6.0</v>
+      </c>
+      <c r="K11" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="L11" s="21" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E12" s="21">
+        <v>7.0</v>
+      </c>
+      <c r="F12" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H12" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I12" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="J12" s="21">
+        <v>7.0</v>
+      </c>
+      <c r="K12" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="L12" s="21" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E13" s="21">
+        <v>8.0</v>
+      </c>
+      <c r="F13" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H13" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I13" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="J13" s="21">
+        <v>8.0</v>
+      </c>
+      <c r="K13" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="L13" s="21" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E14" s="21">
+        <v>9.0</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H14" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I14" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="J14" s="21">
+        <v>9.0</v>
+      </c>
+      <c r="K14" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="L14" s="21" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="C15" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="E15" s="32">
         <v>10.0</v>
       </c>
-      <c r="K3" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="L3" s="29" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="B4" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" s="27" t="s">
+      <c r="F15" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="H15" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="I15" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="J15" s="32">
+        <v>10.0</v>
+      </c>
+      <c r="K15" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="L15" s="32" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E16" s="32">
         <v>11.0</v>
       </c>
-      <c r="F4" s="29" t="s">
+      <c r="F16" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="29" t="s">
+      <c r="G16" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="H4" s="29" t="s">
+      <c r="H16" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="I16" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="I4" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="J4" s="29">
+      <c r="J16" s="32">
         <v>11.0</v>
       </c>
-      <c r="K4" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="L4" s="29" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="B5" s="27" t="s">
-        <v>71</v>
-      </c>
-      <c r="C5" s="27" t="s">
+      <c r="K16" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="L16" s="32" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="B17" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="D17" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E17" s="32">
         <v>12.0</v>
       </c>
-      <c r="F5" s="29" t="s">
+      <c r="F17" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="29" t="s">
+      <c r="G17" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="H5" s="29" t="s">
+      <c r="H17" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="I17" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="I5" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="J5" s="29">
+      <c r="J17" s="32">
         <v>12.0</v>
       </c>
-      <c r="K5" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="L5" s="29" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="C6" s="22" t="s">
+      <c r="K17" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="L17" s="32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="B18" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="D6" s="31" t="s">
+      <c r="D18" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E18" s="21">
         <v>1.0</v>
       </c>
-      <c r="F6" s="20" t="s">
+      <c r="F18" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="20" t="s">
+      <c r="G18" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="H6" s="20" t="s">
+      <c r="H18" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I18" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="I6" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J6" s="20">
+      <c r="J18" s="21">
         <v>1.0</v>
       </c>
-      <c r="K6" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="L6" s="20" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="B7" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" s="22" t="s">
+      <c r="K18" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="L18" s="21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="D7" s="31" t="s">
+      <c r="D19" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E19" s="21">
         <v>2.0</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="F19" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="G7" s="20" t="s">
+      <c r="G19" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="H7" s="20" t="s">
+      <c r="H19" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I19" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="I7" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J7" s="20">
+      <c r="J19" s="21">
         <v>2.0</v>
       </c>
-      <c r="K7" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="L7" s="20" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="B8" s="22" t="s">
-        <v>74</v>
-      </c>
-      <c r="C8" s="22" t="s">
+      <c r="K19" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="L19" s="21" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="B20" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C20" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="D20" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E20" s="21">
         <v>3.0</v>
       </c>
-      <c r="F8" s="20" t="s">
+      <c r="F20" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="G8" s="20" t="s">
+      <c r="G20" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="H8" s="20" t="s">
+      <c r="H20" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I20" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="I8" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J8" s="20">
+      <c r="J20" s="21">
         <v>3.0</v>
       </c>
-      <c r="K8" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="L8" s="20" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="B9" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="C9" s="22" t="s">
+      <c r="K20" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="L20" s="21" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="B21" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="D9" s="31" t="s">
+      <c r="D21" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="E9" s="20">
+      <c r="E21" s="21">
         <v>4.0</v>
       </c>
-      <c r="F9" s="20" t="s">
+      <c r="F21" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="G9" s="20" t="s">
+      <c r="G21" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="H9" s="20" t="s">
+      <c r="H21" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I21" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="I9" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J9" s="20">
+      <c r="J21" s="21">
         <v>4.0</v>
       </c>
-      <c r="K9" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="L9" s="20" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="B10" s="22" t="s">
-        <v>76</v>
-      </c>
-      <c r="C10" s="22" t="s">
+      <c r="K21" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="L21" s="21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="D10" s="31" t="s">
+      <c r="D22" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="E10" s="20">
+      <c r="E22" s="21">
         <v>5.0</v>
       </c>
-      <c r="F10" s="20" t="s">
+      <c r="F22" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="G10" s="20" t="s">
+      <c r="G22" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="H10" s="20" t="s">
+      <c r="H22" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I22" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="I10" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J10" s="20">
+      <c r="J22" s="21">
         <v>5.0</v>
       </c>
-      <c r="K10" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="L10" s="20" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="B11" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="C11" s="22" t="s">
+      <c r="K22" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="L22" s="21" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="B23" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="D11" s="31" t="s">
+      <c r="D23" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="E11" s="20">
+      <c r="E23" s="21">
         <v>6.0</v>
       </c>
-      <c r="F11" s="20" t="s">
+      <c r="F23" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="G11" s="20" t="s">
+      <c r="G23" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="H11" s="20" t="s">
+      <c r="H23" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I23" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="I11" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J11" s="20">
+      <c r="J23" s="21">
         <v>6.0</v>
       </c>
-      <c r="K11" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="L11" s="20" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="B12" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="C12" s="22" t="s">
+      <c r="K23" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="L23" s="21" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="B24" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C24" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="D12" s="31" t="s">
+      <c r="D24" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="E12" s="20">
+      <c r="E24" s="21">
         <v>7.0</v>
       </c>
-      <c r="F12" s="20" t="s">
+      <c r="F24" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="G12" s="20" t="s">
+      <c r="G24" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="H12" s="20" t="s">
+      <c r="H24" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I24" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="I12" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J12" s="20">
+      <c r="J24" s="21">
         <v>7.0</v>
       </c>
-      <c r="K12" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="L12" s="20" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="B13" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="C13" s="22" t="s">
+      <c r="K24" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="L24" s="21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="B25" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="D13" s="31" t="s">
+      <c r="D25" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="E13" s="20">
+      <c r="E25" s="21">
         <v>8.0</v>
       </c>
-      <c r="F13" s="20" t="s">
+      <c r="F25" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="20" t="s">
+      <c r="G25" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="H13" s="20" t="s">
+      <c r="H25" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I25" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="I13" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J13" s="20">
+      <c r="J25" s="21">
         <v>8.0</v>
       </c>
-      <c r="K13" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="L13" s="20" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="B14" s="22" t="s">
-        <v>80</v>
-      </c>
-      <c r="C14" s="22" t="s">
+      <c r="K25" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="L25" s="21" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="B26" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="D14" s="31" t="s">
+      <c r="D26" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="E14" s="20">
+      <c r="E26" s="21">
         <v>9.0</v>
       </c>
-      <c r="F14" s="20" t="s">
+      <c r="F26" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="G14" s="20" t="s">
+      <c r="G26" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="H14" s="20" t="s">
+      <c r="H26" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I26" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="I14" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J14" s="20">
+      <c r="J26" s="21">
         <v>9.0</v>
       </c>
-      <c r="K14" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="L14" s="20" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="B15" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="C15" s="27" t="s">
+      <c r="K26" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="L26" s="21" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="B27" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="C27" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="D15" s="28" t="s">
+      <c r="D27" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E27" s="40">
         <v>10.0</v>
       </c>
-      <c r="F15" s="29" t="s">
+      <c r="F27" s="40" t="s">
+        <v>15</v>
+      </c>
+      <c r="G27" s="40" t="s">
+        <v>66</v>
+      </c>
+      <c r="H27" s="40" t="s">
+        <v>67</v>
+      </c>
+      <c r="I27" s="41" t="s">
+        <v>69</v>
+      </c>
+      <c r="J27" s="40">
+        <v>10.0</v>
+      </c>
+      <c r="K27" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="L27" s="42">
+        <v>45967.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="B28" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="D28" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="E28" s="40">
+        <v>11.0</v>
+      </c>
+      <c r="F28" s="40" t="s">
+        <v>15</v>
+      </c>
+      <c r="G28" s="40" t="s">
+        <v>66</v>
+      </c>
+      <c r="H28" s="40" t="s">
+        <v>67</v>
+      </c>
+      <c r="I28" s="41" t="s">
+        <v>69</v>
+      </c>
+      <c r="J28" s="40">
+        <v>11.0</v>
+      </c>
+      <c r="K28" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="L28" s="42">
+        <v>45967.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="B29" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="C29" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="D29" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="E29" s="40">
+        <v>12.0</v>
+      </c>
+      <c r="F29" s="40" t="s">
+        <v>15</v>
+      </c>
+      <c r="G29" s="40" t="s">
+        <v>66</v>
+      </c>
+      <c r="H29" s="40" t="s">
+        <v>67</v>
+      </c>
+      <c r="I29" s="41" t="s">
+        <v>69</v>
+      </c>
+      <c r="J29" s="40">
+        <v>12.0</v>
+      </c>
+      <c r="K29" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="L29" s="42">
+        <v>45967.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="B30" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D30" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E30" s="21">
+        <v>1.0</v>
+      </c>
+      <c r="F30" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G30" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H30" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I30" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="J30" s="21">
+        <v>1.0</v>
+      </c>
+      <c r="K30" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="L30" s="43">
+        <v>45698.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="B31" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C31" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D31" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E31" s="21">
+        <v>2.0</v>
+      </c>
+      <c r="F31" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G31" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H31" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I31" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="J31" s="21">
+        <v>2.0</v>
+      </c>
+      <c r="K31" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="L31" s="43">
+        <v>45698.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="B32" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C32" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D32" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E32" s="21">
+        <v>3.0</v>
+      </c>
+      <c r="F32" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G32" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H32" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I32" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="J32" s="21">
+        <v>3.0</v>
+      </c>
+      <c r="K32" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="L32" s="43">
+        <v>45698.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="B33" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C33" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D33" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E33" s="21">
+        <v>4.0</v>
+      </c>
+      <c r="F33" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G33" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H33" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I33" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="J33" s="21">
+        <v>4.0</v>
+      </c>
+      <c r="K33" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="L33" s="43">
+        <v>45741.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="B34" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C34" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D34" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E34" s="21">
+        <v>5.0</v>
+      </c>
+      <c r="F34" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G34" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H34" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I34" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="J34" s="21">
+        <v>5.0</v>
+      </c>
+      <c r="K34" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="L34" s="43">
+        <v>45741.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="B35" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C35" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D35" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E35" s="21">
+        <v>6.0</v>
+      </c>
+      <c r="F35" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G35" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H35" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I35" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="J35" s="21">
+        <v>6.0</v>
+      </c>
+      <c r="K35" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="L35" s="43">
+        <v>45741.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="B36" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C36" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D36" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E36" s="21">
+        <v>7.0</v>
+      </c>
+      <c r="F36" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G36" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H36" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I36" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="J36" s="21">
+        <v>7.0</v>
+      </c>
+      <c r="K36" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="L36" s="43">
+        <v>45590.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="B37" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C37" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D37" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E37" s="21">
+        <v>8.0</v>
+      </c>
+      <c r="F37" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G37" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H37" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I37" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="J37" s="21">
+        <v>8.0</v>
+      </c>
+      <c r="K37" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="L37" s="43">
+        <v>45590.0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="B38" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C38" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D38" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E38" s="21">
+        <v>9.0</v>
+      </c>
+      <c r="F38" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G38" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H38" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I38" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="J38" s="21">
+        <v>9.0</v>
+      </c>
+      <c r="K38" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="L38" s="43">
+        <v>45590.0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="B39" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="C39" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="D39" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="E39" s="32">
+        <v>10.0</v>
+      </c>
+      <c r="F39" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G39" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="H39" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="I39" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="J39" s="32">
+        <v>10.0</v>
+      </c>
+      <c r="K39" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="L39" s="32" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="B40" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="C40" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="D40" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="E40" s="32">
+        <v>11.0</v>
+      </c>
+      <c r="F40" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G40" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="H40" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="I40" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="J40" s="32">
+        <v>11.0</v>
+      </c>
+      <c r="K40" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="L40" s="32" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="B41" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="C41" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="D41" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="E41" s="32">
+        <v>12.0</v>
+      </c>
+      <c r="F41" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G41" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="H41" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="I41" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="J41" s="32">
+        <v>12.0</v>
+      </c>
+      <c r="K41" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="L41" s="32" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="B42" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C42" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D42" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E42" s="21">
+        <v>1.0</v>
+      </c>
+      <c r="F42" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G42" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H42" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I42" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="J42" s="21">
+        <v>1.0</v>
+      </c>
+      <c r="K42" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L42" s="21" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="B43" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C43" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D43" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E43" s="21">
+        <v>2.0</v>
+      </c>
+      <c r="F43" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G43" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H43" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I43" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="J43" s="21">
+        <v>2.0</v>
+      </c>
+      <c r="K43" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L43" s="21" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="B44" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C44" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D44" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E44" s="21">
+        <v>3.0</v>
+      </c>
+      <c r="F44" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G44" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H44" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I44" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="J44" s="21">
+        <v>3.0</v>
+      </c>
+      <c r="K44" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L44" s="21" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="B45" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C45" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D45" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E45" s="21">
+        <v>4.0</v>
+      </c>
+      <c r="F45" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G45" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H45" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I45" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="J45" s="21">
+        <v>4.0</v>
+      </c>
+      <c r="K45" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L45" s="21" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="B46" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C46" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D46" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E46" s="21">
+        <v>5.0</v>
+      </c>
+      <c r="F46" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G46" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H46" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I46" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="J46" s="21">
+        <v>5.0</v>
+      </c>
+      <c r="K46" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L46" s="21" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="B47" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C47" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D47" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E47" s="21">
+        <v>6.0</v>
+      </c>
+      <c r="F47" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G47" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H47" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I47" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="J47" s="21">
+        <v>6.0</v>
+      </c>
+      <c r="K47" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L47" s="21" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="B48" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C48" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D48" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E48" s="21">
+        <v>7.0</v>
+      </c>
+      <c r="F48" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G48" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H48" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I48" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="J48" s="21">
+        <v>7.0</v>
+      </c>
+      <c r="K48" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L48" s="21" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="B49" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C49" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D49" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E49" s="21">
+        <v>8.0</v>
+      </c>
+      <c r="F49" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G49" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H49" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I49" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="J49" s="21">
+        <v>8.0</v>
+      </c>
+      <c r="K49" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L49" s="21" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="B50" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C50" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D50" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E50" s="21">
+        <v>9.0</v>
+      </c>
+      <c r="F50" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G50" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H50" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I50" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="J50" s="21">
+        <v>9.0</v>
+      </c>
+      <c r="K50" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L50" s="21" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="B51" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="C51" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="D51" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="E51" s="32">
+        <v>10.0</v>
+      </c>
+      <c r="F51" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="G51" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="H51" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="I51" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="J51" s="32">
+        <v>10.0</v>
+      </c>
+      <c r="K51" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="L51" s="32" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="B52" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="C52" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="D52" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="E52" s="32">
+        <v>11.0</v>
+      </c>
+      <c r="F52" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="G52" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="H52" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="I52" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="J52" s="32">
+        <v>11.0</v>
+      </c>
+      <c r="K52" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="L52" s="32" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="B53" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="C53" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="D53" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="E53" s="32">
+        <v>12.0</v>
+      </c>
+      <c r="F53" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="G53" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="H53" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="I53" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="J53" s="32">
+        <v>12.0</v>
+      </c>
+      <c r="K53" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="L53" s="32" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="B54" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C54" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D54" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E54" s="21">
+        <v>1.0</v>
+      </c>
+      <c r="F54" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="G54" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H54" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I54" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="J54" s="21">
+        <v>1.0</v>
+      </c>
+      <c r="K54" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L54" s="21" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="B55" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C55" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D55" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E55" s="21">
+        <v>2.0</v>
+      </c>
+      <c r="F55" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="G55" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H55" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I55" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="J55" s="21">
+        <v>2.0</v>
+      </c>
+      <c r="K55" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L55" s="21" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="B56" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C56" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D56" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E56" s="21">
+        <v>3.0</v>
+      </c>
+      <c r="F56" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="G56" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H56" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I56" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="J56" s="21">
+        <v>3.0</v>
+      </c>
+      <c r="K56" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L56" s="21" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="B57" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C57" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D57" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E57" s="21">
+        <v>4.0</v>
+      </c>
+      <c r="F57" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="G57" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H57" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I57" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="J57" s="21">
+        <v>4.0</v>
+      </c>
+      <c r="K57" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L57" s="21" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="B58" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C58" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D58" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E58" s="21">
+        <v>5.0</v>
+      </c>
+      <c r="F58" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="G58" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H58" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I58" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="J58" s="21">
+        <v>5.0</v>
+      </c>
+      <c r="K58" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L58" s="21" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="B59" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C59" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D59" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E59" s="21">
+        <v>6.0</v>
+      </c>
+      <c r="F59" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="G59" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H59" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I59" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="J59" s="21">
+        <v>6.0</v>
+      </c>
+      <c r="K59" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L59" s="21" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="B60" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C60" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D60" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E60" s="21">
+        <v>7.0</v>
+      </c>
+      <c r="F60" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="G60" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H60" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I60" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="J60" s="21">
+        <v>7.0</v>
+      </c>
+      <c r="K60" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L60" s="21" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="B61" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C61" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D61" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E61" s="21">
+        <v>8.0</v>
+      </c>
+      <c r="F61" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="G61" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H61" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I61" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="J61" s="21">
+        <v>8.0</v>
+      </c>
+      <c r="K61" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L61" s="21" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="B62" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C62" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D62" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E62" s="21">
+        <v>9.0</v>
+      </c>
+      <c r="F62" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="G62" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H62" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I62" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="J62" s="21">
+        <v>9.0</v>
+      </c>
+      <c r="K62" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="L62" s="21" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="B63" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="C63" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="D63" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="E63" s="32">
+        <v>1.0</v>
+      </c>
+      <c r="F63" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="G63" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="H63" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="I63" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="J63" s="44">
+        <v>10.0</v>
+      </c>
+      <c r="K63" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="G15" s="29" t="s">
+      <c r="L63" s="32" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="B64" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="H15" s="29" t="s">
-        <v>69</v>
-      </c>
-      <c r="I15" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="J15" s="29">
+      <c r="C64" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="D64" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="E64" s="32">
+        <v>1.0</v>
+      </c>
+      <c r="F64" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="G64" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="H64" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="I64" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="J64" s="44">
+        <v>11.0</v>
+      </c>
+      <c r="K64" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="L64" s="32" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="B65" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="C65" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="D65" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="E65" s="45">
+        <v>1.0</v>
+      </c>
+      <c r="F65" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="G65" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="H65" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="I65" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="J65" s="44">
+        <v>12.0</v>
+      </c>
+      <c r="K65" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="L65" s="32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="B66" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="C66" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="D66" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="E66" s="32">
+        <v>1.0</v>
+      </c>
+      <c r="F66" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="G66" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="H66" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="I66" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="J66" s="44">
         <v>10.0</v>
       </c>
-      <c r="K15" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="L15" s="29" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="B16" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="C16" s="27" t="s">
+      <c r="K66" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="L66" s="32">
+        <v>60.0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="B67" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="C67" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="D16" s="28" t="s">
+      <c r="D67" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="E67" s="32">
+        <v>1.0</v>
+      </c>
+      <c r="F67" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="G67" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="H67" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="I67" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="E16" s="29">
+      <c r="J67" s="44">
         <v>11.0</v>
       </c>
-      <c r="F16" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="G16" s="29" t="s">
+      <c r="K67" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="L67" s="32">
+        <v>49.0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="B68" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="H16" s="29" t="s">
-        <v>69</v>
-      </c>
-      <c r="I16" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="J16" s="29">
+      <c r="C68" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="D68" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="E68" s="45">
+        <v>1.0</v>
+      </c>
+      <c r="F68" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="G68" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="H68" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="I68" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="J68" s="44">
+        <v>12.0</v>
+      </c>
+      <c r="K68" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="L68" s="32">
+        <v>131.0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="B69" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="C69" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="D69" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="E69" s="32">
+        <v>1.0</v>
+      </c>
+      <c r="F69" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="G69" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="H69" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="I69" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="J69" s="44">
+        <v>10.0</v>
+      </c>
+      <c r="K69" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="L69" s="32">
+        <v>55.0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="B70" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="C70" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="D70" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="E70" s="32">
+        <v>1.0</v>
+      </c>
+      <c r="F70" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="G70" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="H70" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="I70" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="J70" s="44">
         <v>11.0</v>
       </c>
-      <c r="K16" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="L16" s="29" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="B17" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="C17" s="27" t="s">
+      <c r="K70" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="L70" s="32">
+        <v>48.0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="B71" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="C71" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="D17" s="28" t="s">
+      <c r="D71" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="E71" s="45">
+        <v>1.0</v>
+      </c>
+      <c r="F71" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="G71" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="H71" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="I71" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="E17" s="29">
+      <c r="J71" s="44">
         <v>12.0</v>
       </c>
-      <c r="F17" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17" s="29" t="s">
+      <c r="K71" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="L71" s="32">
+        <v>129.0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="B72" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="H17" s="29" t="s">
-        <v>69</v>
-      </c>
-      <c r="I17" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="J17" s="29">
+      <c r="C72" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="D72" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="E72" s="32">
+        <v>1.0</v>
+      </c>
+      <c r="F72" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="G72" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="H72" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="I72" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="J72" s="44">
+        <v>10.0</v>
+      </c>
+      <c r="K72" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="L72" s="32" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="B73" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="C73" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="D73" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="E73" s="32">
+        <v>1.0</v>
+      </c>
+      <c r="F73" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="G73" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="H73" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="I73" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="J73" s="44">
+        <v>11.0</v>
+      </c>
+      <c r="K73" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="L73" s="32" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="B74" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="C74" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="D74" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="E74" s="45">
+        <v>1.0</v>
+      </c>
+      <c r="F74" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="G74" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="H74" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="I74" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="J74" s="44">
         <v>12.0</v>
       </c>
-      <c r="K17" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="L17" s="29" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="20" t="s">
-        <v>85</v>
-      </c>
-      <c r="B18" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="C18" s="22" t="s">
+      <c r="K74" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="L74" s="32" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="B75" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="C75" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="D18" s="31" t="s">
+      <c r="D75" s="39" t="s">
+        <v>130</v>
+      </c>
+      <c r="E75" s="46">
+        <v>1.0</v>
+      </c>
+      <c r="F75" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="G75" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="H75" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="I75" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="E18" s="20">
+      <c r="J75" s="47">
+        <v>10.0</v>
+      </c>
+      <c r="K75" s="40" t="s">
+        <v>15</v>
+      </c>
+      <c r="L75" s="42">
+        <v>45967.0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="B76" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="C76" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="D76" s="39" t="s">
+        <v>130</v>
+      </c>
+      <c r="E76" s="46">
         <v>1.0</v>
       </c>
-      <c r="F18" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18" s="20" t="s">
+      <c r="F76" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="G76" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="H18" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="I18" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J18" s="20">
+      <c r="H76" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="I76" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="J76" s="47">
+        <v>11.0</v>
+      </c>
+      <c r="K76" s="40" t="s">
+        <v>15</v>
+      </c>
+      <c r="L76" s="42">
+        <v>45967.0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="B77" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="C77" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="D77" s="39" t="s">
+        <v>130</v>
+      </c>
+      <c r="E77" s="46">
         <v>1.0</v>
       </c>
-      <c r="K18" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="L18" s="20" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="B19" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="C19" s="22" t="s">
+      <c r="F77" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="G77" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="H77" s="37" t="s">
         <v>67</v>
       </c>
-      <c r="D19" s="31" t="s">
+      <c r="I77" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="E19" s="20">
+      <c r="J77" s="48">
+        <v>12.0</v>
+      </c>
+      <c r="K77" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="L77" s="49">
+        <v>45967.0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="B78" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C78" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D78" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E78" s="50">
+        <v>1.0</v>
+      </c>
+      <c r="F78" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G78" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="H78" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="I78" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="J78" s="50">
+        <v>1.0</v>
+      </c>
+      <c r="K78" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="L78" s="51">
+        <v>0.3507</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="B79" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C79" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D79" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E79" s="50">
         <v>2.0</v>
       </c>
-      <c r="F19" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="G19" s="20" t="s">
+      <c r="F79" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G79" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="H19" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="I19" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J19" s="20">
+      <c r="H79" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="I79" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="J79" s="50">
         <v>2.0</v>
       </c>
-      <c r="K19" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="L19" s="20" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="B20" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="C20" s="22" t="s">
+      <c r="K79" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="L79" s="51">
+        <v>0.5845</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="B80" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C80" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="D20" s="31" t="s">
+      <c r="D80" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="E20" s="20">
+      <c r="E80" s="50">
         <v>3.0</v>
       </c>
-      <c r="F20" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="G20" s="20" t="s">
+      <c r="F80" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G80" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="H20" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="I20" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J20" s="20">
+      <c r="H80" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="I80" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="J80" s="50">
         <v>3.0</v>
       </c>
-      <c r="K20" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="L20" s="20" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="B21" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="C21" s="22" t="s">
+      <c r="K80" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="L80" s="52">
+        <v>0.8016</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="B81" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C81" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="D21" s="31" t="s">
+      <c r="D81" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="E21" s="20">
+      <c r="E81" s="50">
         <v>4.0</v>
       </c>
-      <c r="F21" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="G21" s="20" t="s">
+      <c r="F81" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G81" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="H21" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="I21" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J21" s="20">
+      <c r="H81" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="I81" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="J81" s="50">
         <v>4.0</v>
       </c>
-      <c r="K21" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="L21" s="20" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="20" t="s">
-        <v>89</v>
-      </c>
-      <c r="B22" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="C22" s="22" t="s">
+      <c r="K81" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="L81" s="51">
+        <v>0.5344</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="24" t="s">
+        <v>150</v>
+      </c>
+      <c r="B82" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C82" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="D22" s="31" t="s">
+      <c r="D82" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="E22" s="20">
+      <c r="E82" s="50">
         <v>5.0</v>
       </c>
-      <c r="F22" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="G22" s="20" t="s">
+      <c r="F82" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G82" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="H22" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="I22" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J22" s="20">
+      <c r="H82" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="I82" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="J82" s="50">
         <v>5.0</v>
       </c>
-      <c r="K22" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="L22" s="20" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="B23" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="C23" s="22" t="s">
+      <c r="K82" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="L82" s="51">
+        <v>0.7181</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="B83" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C83" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="D23" s="31" t="s">
+      <c r="D83" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="E23" s="20">
+      <c r="E83" s="50">
         <v>6.0</v>
       </c>
-      <c r="F23" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="G23" s="20" t="s">
+      <c r="F83" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G83" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="H23" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="I23" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J23" s="20">
+      <c r="H83" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="I83" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="J83" s="50">
         <v>6.0</v>
       </c>
-      <c r="K23" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="L23" s="20" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="20" t="s">
-        <v>91</v>
-      </c>
-      <c r="B24" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="C24" s="22" t="s">
+      <c r="K83" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="L83" s="52">
+        <v>1.7869</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="24" t="s">
+        <v>152</v>
+      </c>
+      <c r="B84" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C84" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="D24" s="31" t="s">
+      <c r="D84" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="E24" s="20">
+      <c r="E84" s="50">
         <v>7.0</v>
       </c>
-      <c r="F24" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="G24" s="20" t="s">
+      <c r="F84" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G84" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="H24" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="I24" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J24" s="20">
+      <c r="H84" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="I84" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="J84" s="50">
         <v>7.0</v>
       </c>
-      <c r="K24" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="L24" s="20" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="B25" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="C25" s="22" t="s">
+      <c r="K84" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="L84" s="51">
+        <v>0.8684</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="24" t="s">
+        <v>153</v>
+      </c>
+      <c r="B85" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C85" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="D25" s="31" t="s">
+      <c r="D85" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="E25" s="20">
+      <c r="E85" s="50">
         <v>8.0</v>
       </c>
-      <c r="F25" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="G25" s="20" t="s">
+      <c r="F85" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G85" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="H25" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="I25" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J25" s="20">
+      <c r="H85" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="I85" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="J85" s="50">
         <v>8.0</v>
       </c>
-      <c r="K25" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="L25" s="20" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="20" t="s">
-        <v>93</v>
-      </c>
-      <c r="B26" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="C26" s="22" t="s">
+      <c r="K85" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="L85" s="51">
+        <v>0.7848999999999999</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="24" t="s">
+        <v>154</v>
+      </c>
+      <c r="B86" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C86" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="D26" s="31" t="s">
+      <c r="D86" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="E26" s="20">
+      <c r="E86" s="50">
         <v>9.0</v>
       </c>
-      <c r="F26" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="G26" s="20" t="s">
+      <c r="F86" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G86" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="H26" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="I26" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J26" s="20">
+      <c r="H86" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="I86" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="J86" s="50">
         <v>9.0</v>
       </c>
-      <c r="K26" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="L26" s="20" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="B27" s="33" t="s">
-        <v>93</v>
-      </c>
-      <c r="C27" s="33" t="s">
+      <c r="K86" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="L86" s="52">
+        <v>2.1376</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="24" t="s">
+        <v>155</v>
+      </c>
+      <c r="B87" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C87" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="D27" s="34" t="s">
+      <c r="D87" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="E27" s="35">
+      <c r="E87" s="50">
         <v>10.0</v>
       </c>
-      <c r="F27" s="35" t="s">
-        <v>15</v>
-      </c>
-      <c r="G27" s="35" t="s">
+      <c r="F87" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G87" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="H27" s="35" t="s">
-        <v>69</v>
-      </c>
-      <c r="I27" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="J27" s="35">
+      <c r="H87" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="I87" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="J87" s="50">
         <v>10.0</v>
       </c>
-      <c r="K27" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="L27" s="37">
-        <v>45967.0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="B28" s="33" t="s">
-        <v>94</v>
-      </c>
-      <c r="C28" s="33" t="s">
+      <c r="K87" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="L87" s="51">
+        <v>1.002</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="24" t="s">
+        <v>156</v>
+      </c>
+      <c r="B88" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C88" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="D28" s="34" t="s">
+      <c r="D88" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="E28" s="35">
+      <c r="E88" s="50">
         <v>11.0</v>
       </c>
-      <c r="F28" s="35" t="s">
-        <v>15</v>
-      </c>
-      <c r="G28" s="35" t="s">
+      <c r="F88" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G88" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="H28" s="35" t="s">
-        <v>69</v>
-      </c>
-      <c r="I28" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="J28" s="35">
+      <c r="H88" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="I88" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="J88" s="50">
         <v>11.0</v>
       </c>
-      <c r="K28" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="L28" s="37">
-        <v>45967.0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="B29" s="33" t="s">
-        <v>95</v>
-      </c>
-      <c r="C29" s="33" t="s">
+      <c r="K88" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="L88" s="51">
+        <v>0.8183</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="24" t="s">
+        <v>157</v>
+      </c>
+      <c r="B89" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C89" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="D29" s="34" t="s">
+      <c r="D89" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="E29" s="35">
+      <c r="E89" s="50">
         <v>12.0</v>
       </c>
-      <c r="F29" s="35" t="s">
-        <v>15</v>
-      </c>
-      <c r="G29" s="35" t="s">
+      <c r="F89" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G89" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="H29" s="35" t="s">
-        <v>69</v>
-      </c>
-      <c r="I29" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="J29" s="35">
+      <c r="H89" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="I89" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="J89" s="50">
         <v>12.0</v>
       </c>
-      <c r="K29" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="L29" s="37">
-        <v>45967.0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="B30" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="C30" s="22" t="s">
+      <c r="K89" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="L89" s="52">
+        <v>2.1877</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="24" t="s">
+        <v>158</v>
+      </c>
+      <c r="B90" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C90" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="D30" s="31" t="s">
+      <c r="D90" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="E30" s="20">
+      <c r="E90" s="50">
         <v>1.0</v>
       </c>
-      <c r="F30" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="G30" s="20" t="s">
+      <c r="F90" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G90" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="H30" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="I30" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J30" s="20">
+      <c r="H90" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="I90" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="J90" s="50">
         <v>1.0</v>
       </c>
-      <c r="K30" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="L30" s="38">
-        <v>45332.0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="B31" s="22" t="s">
-        <v>97</v>
-      </c>
-      <c r="C31" s="22" t="s">
+      <c r="K90" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="L90" s="21" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="24" t="s">
+        <v>159</v>
+      </c>
+      <c r="B91" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C91" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="D31" s="31" t="s">
+      <c r="D91" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="E31" s="20">
+      <c r="E91" s="50">
         <v>2.0</v>
       </c>
-      <c r="F31" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="G31" s="20" t="s">
+      <c r="F91" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G91" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="H31" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="I31" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J31" s="20">
+      <c r="H91" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="I91" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="J91" s="50">
         <v>2.0</v>
       </c>
-      <c r="K31" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="L31" s="38">
-        <v>45332.0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="B32" s="22" t="s">
-        <v>98</v>
-      </c>
-      <c r="C32" s="22" t="s">
+      <c r="K91" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="L91" s="21" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="24" t="s">
+        <v>160</v>
+      </c>
+      <c r="B92" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C92" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="D32" s="31" t="s">
+      <c r="D92" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="E32" s="20">
+      <c r="E92" s="50">
         <v>3.0</v>
       </c>
-      <c r="F32" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="G32" s="20" t="s">
+      <c r="F92" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G92" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="H32" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="I32" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J32" s="20">
+      <c r="H92" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="I92" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="J92" s="50">
         <v>3.0</v>
       </c>
-      <c r="K32" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="L32" s="38">
-        <v>45332.0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="B33" s="22" t="s">
-        <v>99</v>
-      </c>
-      <c r="C33" s="22" t="s">
+      <c r="K92" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="L92" s="24" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="B93" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C93" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="D33" s="31" t="s">
+      <c r="D93" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="E33" s="20">
+      <c r="E93" s="50">
         <v>4.0</v>
       </c>
-      <c r="F33" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="G33" s="20" t="s">
+      <c r="F93" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G93" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="H33" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="I33" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J33" s="20">
+      <c r="H93" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="I93" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="J93" s="50">
         <v>4.0</v>
       </c>
-      <c r="K33" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="L33" s="38">
-        <v>45741.0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="B34" s="22" t="s">
-        <v>100</v>
-      </c>
-      <c r="C34" s="22" t="s">
+      <c r="K93" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="L93" s="21" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="24" t="s">
+        <v>162</v>
+      </c>
+      <c r="B94" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C94" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="D34" s="31" t="s">
+      <c r="D94" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="E34" s="20">
+      <c r="E94" s="50">
         <v>5.0</v>
       </c>
-      <c r="F34" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="G34" s="20" t="s">
+      <c r="F94" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G94" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="H34" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="I34" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J34" s="20">
+      <c r="H94" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="I94" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="J94" s="50">
         <v>5.0</v>
       </c>
-      <c r="K34" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="L34" s="38">
-        <v>45741.0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="B35" s="22" t="s">
-        <v>101</v>
-      </c>
-      <c r="C35" s="22" t="s">
+      <c r="K94" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="L94" s="21" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="B95" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C95" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="D35" s="31" t="s">
+      <c r="D95" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="E35" s="20">
+      <c r="E95" s="50">
         <v>6.0</v>
       </c>
-      <c r="F35" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="G35" s="20" t="s">
+      <c r="F95" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G95" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="H35" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="I35" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J35" s="20">
+      <c r="H95" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="I95" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="J95" s="50">
         <v>6.0</v>
       </c>
-      <c r="K35" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="L35" s="38">
-        <v>45741.0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="20" t="s">
-        <v>103</v>
-      </c>
-      <c r="B36" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="C36" s="22" t="s">
+      <c r="K95" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="L95" s="24" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="B96" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C96" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="D36" s="31" t="s">
+      <c r="D96" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="E36" s="20">
+      <c r="E96" s="50">
         <v>7.0</v>
       </c>
-      <c r="F36" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="G36" s="20" t="s">
+      <c r="F96" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G96" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="H36" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="I36" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J36" s="20">
+      <c r="H96" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="I96" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="J96" s="50">
         <v>7.0</v>
       </c>
-      <c r="K36" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="L36" s="38">
-        <v>45590.0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="B37" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="C37" s="22" t="s">
+      <c r="K96" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="L96" s="21" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="24" t="s">
+        <v>165</v>
+      </c>
+      <c r="B97" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C97" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="D37" s="31" t="s">
+      <c r="D97" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="E37" s="20">
+      <c r="E97" s="50">
         <v>8.0</v>
       </c>
-      <c r="F37" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="G37" s="20" t="s">
+      <c r="F97" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G97" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="H37" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="I37" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J37" s="20">
+      <c r="H97" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="I97" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="J97" s="50">
         <v>8.0</v>
       </c>
-      <c r="K37" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="L37" s="38">
-        <v>45590.0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="B38" s="22" t="s">
-        <v>104</v>
-      </c>
-      <c r="C38" s="22" t="s">
+      <c r="K97" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="L97" s="21" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="24" t="s">
+        <v>166</v>
+      </c>
+      <c r="B98" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C98" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="D38" s="31" t="s">
+      <c r="D98" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="E38" s="20">
+      <c r="E98" s="50">
         <v>9.0</v>
       </c>
-      <c r="F38" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="G38" s="20" t="s">
+      <c r="F98" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G98" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="H38" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="I38" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J38" s="20">
+      <c r="H98" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="I98" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="J98" s="50">
         <v>9.0</v>
       </c>
-      <c r="K38" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="L38" s="38">
-        <v>45590.0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="B39" s="27" t="s">
-        <v>105</v>
-      </c>
-      <c r="C39" s="27" t="s">
+      <c r="K98" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="L98" s="21" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="B99" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C99" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="D39" s="28" t="s">
+      <c r="D99" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="E39" s="29">
+      <c r="E99" s="50">
         <v>10.0</v>
       </c>
-      <c r="F39" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="G39" s="29" t="s">
+      <c r="F99" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G99" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="H39" s="29" t="s">
-        <v>69</v>
-      </c>
-      <c r="I39" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="J39" s="29">
+      <c r="H99" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="I99" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="J99" s="50">
         <v>10.0</v>
       </c>
-      <c r="K39" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="L39" s="29" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="B40" s="27" t="s">
-        <v>106</v>
-      </c>
-      <c r="C40" s="27" t="s">
+      <c r="K99" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="L99" s="21" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="B100" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C100" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="D40" s="28" t="s">
+      <c r="D100" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="E40" s="29">
+      <c r="E100" s="50">
         <v>11.0</v>
       </c>
-      <c r="F40" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="G40" s="29" t="s">
+      <c r="F100" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G100" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="H40" s="29" t="s">
-        <v>69</v>
-      </c>
-      <c r="I40" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="J40" s="29">
+      <c r="H100" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="I100" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="J100" s="50">
         <v>11.0</v>
       </c>
-      <c r="K40" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="L40" s="29" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="B41" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="C41" s="27" t="s">
+      <c r="K100" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="L100" s="21" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="B101" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C101" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="D41" s="28" t="s">
+      <c r="D101" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="E41" s="29">
+      <c r="E101" s="50">
         <v>12.0</v>
       </c>
-      <c r="F41" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="G41" s="29" t="s">
+      <c r="F101" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G101" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="H41" s="29" t="s">
-        <v>69</v>
-      </c>
-      <c r="I41" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="J41" s="29">
+      <c r="H101" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="I101" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="J101" s="50">
         <v>12.0</v>
       </c>
-      <c r="K41" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="L41" s="29" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="B42" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="C42" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D42" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E42" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="F42" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="G42" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="H42" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="I42" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J42" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="K42" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="L42" s="20" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="B43" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="C43" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D43" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E43" s="20">
-        <v>2.0</v>
-      </c>
-      <c r="F43" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="G43" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="H43" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="I43" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J43" s="20">
-        <v>2.0</v>
-      </c>
-      <c r="K43" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="L43" s="20" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="20" t="s">
-        <v>111</v>
-      </c>
-      <c r="B44" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="C44" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D44" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E44" s="20">
-        <v>3.0</v>
-      </c>
-      <c r="F44" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="G44" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="H44" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="I44" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J44" s="20">
-        <v>3.0</v>
-      </c>
-      <c r="K44" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="L44" s="20" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="B45" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="C45" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D45" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E45" s="20">
-        <v>4.0</v>
-      </c>
-      <c r="F45" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="G45" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="H45" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="I45" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J45" s="20">
-        <v>4.0</v>
-      </c>
-      <c r="K45" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="L45" s="20" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="B46" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="C46" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D46" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E46" s="20">
-        <v>5.0</v>
-      </c>
-      <c r="F46" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="G46" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="H46" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="I46" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J46" s="20">
-        <v>5.0</v>
-      </c>
-      <c r="K46" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="L46" s="20" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="20" t="s">
-        <v>114</v>
-      </c>
-      <c r="B47" s="22" t="s">
-        <v>113</v>
-      </c>
-      <c r="C47" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D47" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E47" s="20">
-        <v>6.0</v>
-      </c>
-      <c r="F47" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="G47" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="H47" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="I47" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J47" s="20">
-        <v>6.0</v>
-      </c>
-      <c r="K47" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="L47" s="20" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="B48" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="C48" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D48" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E48" s="20">
-        <v>7.0</v>
-      </c>
-      <c r="F48" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="G48" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="H48" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="I48" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J48" s="20">
-        <v>7.0</v>
-      </c>
-      <c r="K48" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="L48" s="20" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="20" t="s">
-        <v>116</v>
-      </c>
-      <c r="B49" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="C49" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D49" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E49" s="20">
-        <v>8.0</v>
-      </c>
-      <c r="F49" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="G49" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="H49" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="I49" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J49" s="20">
-        <v>8.0</v>
-      </c>
-      <c r="K49" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="L49" s="20" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="B50" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="C50" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D50" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E50" s="20">
-        <v>9.0</v>
-      </c>
-      <c r="F50" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="G50" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="H50" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="I50" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J50" s="20">
-        <v>9.0</v>
-      </c>
-      <c r="K50" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="L50" s="20" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="B51" s="27" t="s">
-        <v>117</v>
-      </c>
-      <c r="C51" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="D51" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="E51" s="29">
-        <v>10.0</v>
-      </c>
-      <c r="F51" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="G51" s="29" t="s">
-        <v>66</v>
-      </c>
-      <c r="H51" s="29" t="s">
-        <v>69</v>
-      </c>
-      <c r="I51" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="J51" s="29">
-        <v>10.0</v>
-      </c>
-      <c r="K51" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="L51" s="29" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="20" t="s">
-        <v>119</v>
-      </c>
-      <c r="B52" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="C52" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="D52" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="E52" s="29">
-        <v>11.0</v>
-      </c>
-      <c r="F52" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="G52" s="29" t="s">
-        <v>66</v>
-      </c>
-      <c r="H52" s="29" t="s">
-        <v>69</v>
-      </c>
-      <c r="I52" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="J52" s="29">
-        <v>11.0</v>
-      </c>
-      <c r="K52" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="L52" s="29" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="B53" s="27" t="s">
-        <v>119</v>
-      </c>
-      <c r="C53" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="D53" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="E53" s="29">
-        <v>12.0</v>
-      </c>
-      <c r="F53" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="G53" s="29" t="s">
-        <v>66</v>
-      </c>
-      <c r="H53" s="29" t="s">
-        <v>69</v>
-      </c>
-      <c r="I53" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="J53" s="29">
-        <v>12.0</v>
-      </c>
-      <c r="K53" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="L53" s="29" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="B54" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="C54" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D54" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E54" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="F54" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G54" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="H54" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="I54" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J54" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="K54" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="L54" s="20" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="B55" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="C55" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D55" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E55" s="20">
-        <v>2.0</v>
-      </c>
-      <c r="F55" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G55" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="H55" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="I55" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J55" s="20">
-        <v>2.0</v>
-      </c>
-      <c r="K55" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="L55" s="20" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="B56" s="22" t="s">
-        <v>122</v>
-      </c>
-      <c r="C56" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D56" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E56" s="20">
-        <v>3.0</v>
-      </c>
-      <c r="F56" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G56" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="H56" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="I56" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J56" s="20">
-        <v>3.0</v>
-      </c>
-      <c r="K56" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="L56" s="20" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="B57" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="C57" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D57" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E57" s="20">
-        <v>4.0</v>
-      </c>
-      <c r="F57" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G57" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="H57" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="I57" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J57" s="20">
-        <v>4.0</v>
-      </c>
-      <c r="K57" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="L57" s="20" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="B58" s="22" t="s">
-        <v>124</v>
-      </c>
-      <c r="C58" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D58" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E58" s="20">
-        <v>5.0</v>
-      </c>
-      <c r="F58" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G58" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="H58" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="I58" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J58" s="20">
-        <v>5.0</v>
-      </c>
-      <c r="K58" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="L58" s="20" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="B59" s="22" t="s">
-        <v>125</v>
-      </c>
-      <c r="C59" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D59" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E59" s="20">
-        <v>6.0</v>
-      </c>
-      <c r="F59" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G59" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="H59" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="I59" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J59" s="20">
-        <v>6.0</v>
-      </c>
-      <c r="K59" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="L59" s="20" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="B60" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="C60" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D60" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E60" s="20">
-        <v>7.0</v>
-      </c>
-      <c r="F60" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G60" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="H60" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="I60" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J60" s="20">
-        <v>7.0</v>
-      </c>
-      <c r="K60" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="L60" s="20" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="B61" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="C61" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D61" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E61" s="20">
-        <v>8.0</v>
-      </c>
-      <c r="F61" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G61" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="H61" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="I61" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J61" s="20">
-        <v>8.0</v>
-      </c>
-      <c r="K61" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="L61" s="20" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="B62" s="22" t="s">
-        <v>128</v>
-      </c>
-      <c r="C62" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D62" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E62" s="20">
-        <v>9.0</v>
-      </c>
-      <c r="F62" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G62" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="H62" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="I62" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J62" s="20">
-        <v>9.0</v>
-      </c>
-      <c r="K62" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="L62" s="20" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="B63" s="27" t="s">
-        <v>129</v>
-      </c>
-      <c r="C63" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="D63" s="30" t="s">
-        <v>131</v>
-      </c>
-      <c r="E63" s="29">
-        <v>1.0</v>
-      </c>
-      <c r="F63" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="G63" s="29" t="s">
-        <v>66</v>
-      </c>
-      <c r="H63" s="29" t="s">
-        <v>69</v>
-      </c>
-      <c r="I63" s="30" t="s">
-        <v>68</v>
-      </c>
-      <c r="J63" s="29">
-        <v>9.0</v>
-      </c>
-      <c r="K63" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="L63" s="29" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="B64" s="27" t="s">
-        <v>130</v>
-      </c>
-      <c r="C64" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="D64" s="30" t="s">
-        <v>131</v>
-      </c>
-      <c r="E64" s="29">
-        <v>1.0</v>
-      </c>
-      <c r="F64" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="G64" s="29" t="s">
-        <v>66</v>
-      </c>
-      <c r="H64" s="29" t="s">
-        <v>69</v>
-      </c>
-      <c r="I64" s="30" t="s">
-        <v>68</v>
-      </c>
-      <c r="J64" s="29">
-        <v>10.0</v>
-      </c>
-      <c r="K64" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="L64" s="29" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="B65" s="27" t="s">
-        <v>132</v>
-      </c>
-      <c r="C65" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="D65" s="30" t="s">
-        <v>131</v>
-      </c>
-      <c r="E65" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="F65" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="G65" s="27" t="s">
-        <v>66</v>
-      </c>
-      <c r="H65" s="27" t="s">
-        <v>69</v>
-      </c>
-      <c r="I65" s="30" t="s">
-        <v>68</v>
-      </c>
-      <c r="J65" s="29">
-        <v>11.0</v>
-      </c>
-      <c r="K65" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="L65" s="29" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="B66" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="C66" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="D66" s="30" t="s">
-        <v>131</v>
-      </c>
-      <c r="E66" s="29">
-        <v>1.0</v>
-      </c>
-      <c r="F66" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="G66" s="29" t="s">
-        <v>66</v>
-      </c>
-      <c r="H66" s="29" t="s">
-        <v>69</v>
-      </c>
-      <c r="I66" s="30" t="s">
-        <v>68</v>
-      </c>
-      <c r="J66" s="29">
-        <v>9.0</v>
-      </c>
-      <c r="K66" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="L66" s="29">
-        <v>60.0</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="B67" s="27" t="s">
-        <v>134</v>
-      </c>
-      <c r="C67" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="D67" s="30" t="s">
-        <v>131</v>
-      </c>
-      <c r="E67" s="29">
-        <v>1.0</v>
-      </c>
-      <c r="F67" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="G67" s="29" t="s">
-        <v>66</v>
-      </c>
-      <c r="H67" s="29" t="s">
-        <v>69</v>
-      </c>
-      <c r="I67" s="30" t="s">
-        <v>68</v>
-      </c>
-      <c r="J67" s="29">
-        <v>10.0</v>
-      </c>
-      <c r="K67" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="L67" s="29">
-        <v>49.0</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="22" t="s">
-        <v>136</v>
-      </c>
-      <c r="B68" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="C68" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="D68" s="30" t="s">
-        <v>131</v>
-      </c>
-      <c r="E68" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="F68" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="G68" s="27" t="s">
-        <v>66</v>
-      </c>
-      <c r="H68" s="27" t="s">
-        <v>69</v>
-      </c>
-      <c r="I68" s="30" t="s">
-        <v>68</v>
-      </c>
-      <c r="J68" s="29">
-        <v>11.0</v>
-      </c>
-      <c r="K68" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="L68" s="29">
-        <v>131.0</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="B69" s="27" t="s">
-        <v>136</v>
-      </c>
-      <c r="C69" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="D69" s="30" t="s">
-        <v>131</v>
-      </c>
-      <c r="E69" s="29">
-        <v>1.0</v>
-      </c>
-      <c r="F69" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="G69" s="29" t="s">
-        <v>66</v>
-      </c>
-      <c r="H69" s="29" t="s">
-        <v>69</v>
-      </c>
-      <c r="I69" s="30" t="s">
-        <v>68</v>
-      </c>
-      <c r="J69" s="29">
-        <v>9.0</v>
-      </c>
-      <c r="K69" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="L69" s="29">
-        <v>55.0</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="B70" s="27" t="s">
-        <v>137</v>
-      </c>
-      <c r="C70" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="D70" s="30" t="s">
-        <v>131</v>
-      </c>
-      <c r="E70" s="29">
-        <v>1.0</v>
-      </c>
-      <c r="F70" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="G70" s="29" t="s">
-        <v>66</v>
-      </c>
-      <c r="H70" s="29" t="s">
-        <v>69</v>
-      </c>
-      <c r="I70" s="30" t="s">
-        <v>68</v>
-      </c>
-      <c r="J70" s="29">
-        <v>10.0</v>
-      </c>
-      <c r="K70" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="L70" s="29">
-        <v>48.0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="B71" s="27" t="s">
-        <v>138</v>
-      </c>
-      <c r="C71" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="D71" s="30" t="s">
-        <v>131</v>
-      </c>
-      <c r="E71" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="F71" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="G71" s="27" t="s">
-        <v>66</v>
-      </c>
-      <c r="H71" s="27" t="s">
-        <v>69</v>
-      </c>
-      <c r="I71" s="30" t="s">
-        <v>68</v>
-      </c>
-      <c r="J71" s="29">
-        <v>11.0</v>
-      </c>
-      <c r="K71" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="L71" s="29">
-        <v>129.0</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="20" t="s">
-        <v>140</v>
-      </c>
-      <c r="B72" s="27" t="s">
-        <v>139</v>
-      </c>
-      <c r="C72" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="D72" s="30" t="s">
-        <v>131</v>
-      </c>
-      <c r="E72" s="29">
-        <v>1.0</v>
-      </c>
-      <c r="F72" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="G72" s="29" t="s">
-        <v>66</v>
-      </c>
-      <c r="H72" s="29" t="s">
-        <v>69</v>
-      </c>
-      <c r="I72" s="30" t="s">
-        <v>68</v>
-      </c>
-      <c r="J72" s="29">
-        <v>9.0</v>
-      </c>
-      <c r="K72" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="L72" s="29" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="20" t="s">
-        <v>141</v>
-      </c>
-      <c r="B73" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="C73" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="D73" s="30" t="s">
-        <v>131</v>
-      </c>
-      <c r="E73" s="29">
-        <v>1.0</v>
-      </c>
-      <c r="F73" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="G73" s="29" t="s">
-        <v>66</v>
-      </c>
-      <c r="H73" s="29" t="s">
-        <v>69</v>
-      </c>
-      <c r="I73" s="30" t="s">
-        <v>68</v>
-      </c>
-      <c r="J73" s="29">
-        <v>10.0</v>
-      </c>
-      <c r="K73" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="L73" s="29" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="22" t="s">
-        <v>142</v>
-      </c>
-      <c r="B74" s="27" t="s">
-        <v>141</v>
-      </c>
-      <c r="C74" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="D74" s="30" t="s">
-        <v>131</v>
-      </c>
-      <c r="E74" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="F74" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="G74" s="27" t="s">
-        <v>66</v>
-      </c>
-      <c r="H74" s="27" t="s">
-        <v>69</v>
-      </c>
-      <c r="I74" s="30" t="s">
-        <v>68</v>
-      </c>
-      <c r="J74" s="29">
-        <v>11.0</v>
-      </c>
-      <c r="K74" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="L74" s="29" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="22" t="s">
-        <v>143</v>
-      </c>
-      <c r="B75" s="33" t="s">
-        <v>142</v>
-      </c>
-      <c r="C75" s="33" t="s">
-        <v>67</v>
-      </c>
-      <c r="D75" s="34" t="s">
-        <v>131</v>
-      </c>
-      <c r="E75" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="F75" s="33" t="s">
-        <v>144</v>
-      </c>
-      <c r="G75" s="33" t="s">
-        <v>66</v>
-      </c>
-      <c r="H75" s="33" t="s">
-        <v>69</v>
-      </c>
-      <c r="I75" s="34" t="s">
-        <v>68</v>
-      </c>
-      <c r="J75" s="35">
-        <v>9.0</v>
-      </c>
-      <c r="K75" s="35" t="s">
-        <v>15</v>
-      </c>
-      <c r="L75" s="37">
-        <v>45967.0</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="22" t="s">
-        <v>145</v>
-      </c>
-      <c r="B76" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="C76" s="33" t="s">
-        <v>67</v>
-      </c>
-      <c r="D76" s="34" t="s">
-        <v>131</v>
-      </c>
-      <c r="E76" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="F76" s="33" t="s">
-        <v>144</v>
-      </c>
-      <c r="G76" s="33" t="s">
-        <v>66</v>
-      </c>
-      <c r="H76" s="33" t="s">
-        <v>69</v>
-      </c>
-      <c r="I76" s="34" t="s">
-        <v>68</v>
-      </c>
-      <c r="J76" s="35">
-        <v>10.0</v>
-      </c>
-      <c r="K76" s="35" t="s">
-        <v>15</v>
-      </c>
-      <c r="L76" s="37">
-        <v>45967.0</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="22" t="s">
-        <v>146</v>
-      </c>
-      <c r="B77" s="41" t="s">
-        <v>145</v>
-      </c>
-      <c r="C77" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="D77" s="42" t="s">
-        <v>131</v>
-      </c>
-      <c r="E77" s="43">
-        <v>1.0</v>
-      </c>
-      <c r="F77" s="41" t="s">
-        <v>144</v>
-      </c>
-      <c r="G77" s="41" t="s">
-        <v>66</v>
-      </c>
-      <c r="H77" s="41" t="s">
-        <v>69</v>
-      </c>
-      <c r="I77" s="42" t="s">
-        <v>68</v>
-      </c>
-      <c r="J77" s="43">
-        <v>11.0</v>
-      </c>
-      <c r="K77" s="41" t="s">
-        <v>15</v>
-      </c>
-      <c r="L77" s="44">
-        <v>45967.0</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="22" t="s">
-        <v>147</v>
-      </c>
-      <c r="B78" s="22" t="s">
-        <v>146</v>
-      </c>
-      <c r="C78" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D78" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E78" s="45">
-        <v>1.0</v>
-      </c>
-      <c r="F78" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="G78" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="H78" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="I78" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="J78" s="45">
-        <v>1.0</v>
-      </c>
-      <c r="K78" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="L78" s="46">
-        <v>0.3507</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="22" t="s">
-        <v>148</v>
-      </c>
-      <c r="B79" s="22" t="s">
-        <v>147</v>
-      </c>
-      <c r="C79" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D79" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E79" s="45">
-        <v>2.0</v>
-      </c>
-      <c r="F79" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="G79" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="H79" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="I79" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="J79" s="45">
-        <v>2.0</v>
-      </c>
-      <c r="K79" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="L79" s="46">
-        <v>0.5845</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="22" t="s">
-        <v>149</v>
-      </c>
-      <c r="B80" s="22" t="s">
-        <v>148</v>
-      </c>
-      <c r="C80" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D80" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E80" s="45">
-        <v>3.0</v>
-      </c>
-      <c r="F80" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="G80" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="H80" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="I80" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="J80" s="45">
-        <v>3.0</v>
-      </c>
-      <c r="K80" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="L80" s="47">
-        <v>0.8016</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="22" t="s">
-        <v>150</v>
-      </c>
-      <c r="B81" s="22" t="s">
-        <v>149</v>
-      </c>
-      <c r="C81" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D81" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E81" s="45">
-        <v>4.0</v>
-      </c>
-      <c r="F81" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="G81" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="H81" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="I81" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="J81" s="45">
-        <v>4.0</v>
-      </c>
-      <c r="K81" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="L81" s="46">
-        <v>0.5344</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="B82" s="22" t="s">
-        <v>150</v>
-      </c>
-      <c r="C82" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D82" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E82" s="45">
-        <v>5.0</v>
-      </c>
-      <c r="F82" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="G82" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="H82" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="I82" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="J82" s="45">
-        <v>5.0</v>
-      </c>
-      <c r="K82" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="L82" s="46">
-        <v>0.7181</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="22" t="s">
-        <v>152</v>
-      </c>
-      <c r="B83" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="C83" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D83" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E83" s="45">
-        <v>6.0</v>
-      </c>
-      <c r="F83" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="G83" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="H83" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="I83" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="J83" s="45">
-        <v>6.0</v>
-      </c>
-      <c r="K83" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="L83" s="47">
-        <v>1.7869</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="22" t="s">
-        <v>153</v>
-      </c>
-      <c r="B84" s="22" t="s">
-        <v>152</v>
-      </c>
-      <c r="C84" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D84" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E84" s="45">
-        <v>7.0</v>
-      </c>
-      <c r="F84" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="G84" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="H84" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="I84" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="J84" s="45">
-        <v>7.0</v>
-      </c>
-      <c r="K84" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="L84" s="46">
-        <v>0.8684</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="B85" s="22" t="s">
-        <v>153</v>
-      </c>
-      <c r="C85" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D85" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E85" s="45">
-        <v>8.0</v>
-      </c>
-      <c r="F85" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="G85" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="H85" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="I85" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="J85" s="45">
-        <v>8.0</v>
-      </c>
-      <c r="K85" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="L85" s="46">
-        <v>0.7848999999999999</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="22" t="s">
-        <v>155</v>
-      </c>
-      <c r="B86" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="C86" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D86" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E86" s="45">
-        <v>9.0</v>
-      </c>
-      <c r="F86" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="G86" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="H86" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="I86" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="J86" s="45">
-        <v>9.0</v>
-      </c>
-      <c r="K86" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="L86" s="47">
-        <v>2.1376</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="B87" s="22" t="s">
-        <v>155</v>
-      </c>
-      <c r="C87" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D87" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E87" s="45">
-        <v>10.0</v>
-      </c>
-      <c r="F87" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="G87" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="H87" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="I87" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="J87" s="45">
-        <v>10.0</v>
-      </c>
-      <c r="K87" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="L87" s="46">
-        <v>1.002</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="22" t="s">
-        <v>157</v>
-      </c>
-      <c r="B88" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="C88" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D88" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E88" s="45">
-        <v>11.0</v>
-      </c>
-      <c r="F88" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="G88" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="H88" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="I88" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="J88" s="45">
-        <v>11.0</v>
-      </c>
-      <c r="K88" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="L88" s="46">
-        <v>0.8183</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="22" t="s">
-        <v>158</v>
-      </c>
-      <c r="B89" s="22" t="s">
-        <v>157</v>
-      </c>
-      <c r="C89" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D89" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E89" s="45">
-        <v>12.0</v>
-      </c>
-      <c r="F89" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="G89" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="H89" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="I89" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="J89" s="45">
-        <v>12.0</v>
-      </c>
-      <c r="K89" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="L89" s="47">
-        <v>2.1877</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="22" t="s">
-        <v>159</v>
-      </c>
-      <c r="B90" s="22" t="s">
-        <v>158</v>
-      </c>
-      <c r="C90" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D90" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E90" s="45">
-        <v>1.0</v>
-      </c>
-      <c r="F90" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="G90" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="H90" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="I90" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="J90" s="45">
-        <v>1.0</v>
-      </c>
-      <c r="K90" s="20" t="s">
+      <c r="K101" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="L90" s="20" t="s">
+      <c r="L101" s="21" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="22" t="s">
-        <v>160</v>
-      </c>
-      <c r="B91" s="22" t="s">
-        <v>159</v>
-      </c>
-      <c r="C91" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D91" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E91" s="45">
-        <v>2.0</v>
-      </c>
-      <c r="F91" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="G91" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="H91" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="I91" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="J91" s="45">
-        <v>2.0</v>
-      </c>
-      <c r="K91" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="L91" s="20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="22" t="s">
-        <v>161</v>
-      </c>
-      <c r="B92" s="22" t="s">
-        <v>160</v>
-      </c>
-      <c r="C92" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D92" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E92" s="45">
-        <v>3.0</v>
-      </c>
-      <c r="F92" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="G92" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="H92" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="I92" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="J92" s="45">
-        <v>3.0</v>
-      </c>
-      <c r="K92" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="L92" s="22" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="22" t="s">
-        <v>162</v>
-      </c>
-      <c r="B93" s="22" t="s">
-        <v>161</v>
-      </c>
-      <c r="C93" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D93" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E93" s="45">
-        <v>4.0</v>
-      </c>
-      <c r="F93" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="G93" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="H93" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="I93" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="J93" s="45">
-        <v>4.0</v>
-      </c>
-      <c r="K93" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="L93" s="20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="22" t="s">
-        <v>163</v>
-      </c>
-      <c r="B94" s="22" t="s">
-        <v>162</v>
-      </c>
-      <c r="C94" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D94" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E94" s="45">
-        <v>5.0</v>
-      </c>
-      <c r="F94" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="G94" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="H94" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="I94" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="J94" s="45">
-        <v>5.0</v>
-      </c>
-      <c r="K94" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="L94" s="20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="B95" s="22" t="s">
-        <v>163</v>
-      </c>
-      <c r="C95" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D95" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E95" s="45">
-        <v>6.0</v>
-      </c>
-      <c r="F95" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="G95" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="H95" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="I95" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="J95" s="45">
-        <v>6.0</v>
-      </c>
-      <c r="K95" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="L95" s="22" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="22" t="s">
-        <v>165</v>
-      </c>
-      <c r="B96" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="C96" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D96" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E96" s="45">
-        <v>7.0</v>
-      </c>
-      <c r="F96" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="G96" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="H96" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="I96" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="J96" s="45">
-        <v>7.0</v>
-      </c>
-      <c r="K96" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="L96" s="20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="22" t="s">
-        <v>166</v>
-      </c>
-      <c r="B97" s="22" t="s">
-        <v>165</v>
-      </c>
-      <c r="C97" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D97" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E97" s="45">
-        <v>8.0</v>
-      </c>
-      <c r="F97" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="G97" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="H97" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="I97" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="J97" s="45">
-        <v>8.0</v>
-      </c>
-      <c r="K97" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="L97" s="20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="22" t="s">
-        <v>167</v>
-      </c>
-      <c r="B98" s="22" t="s">
-        <v>166</v>
-      </c>
-      <c r="C98" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D98" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E98" s="45">
-        <v>9.0</v>
-      </c>
-      <c r="F98" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="G98" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="H98" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="I98" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="J98" s="45">
-        <v>9.0</v>
-      </c>
-      <c r="K98" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="L98" s="20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="22" t="s">
-        <v>168</v>
-      </c>
-      <c r="B99" s="22" t="s">
-        <v>167</v>
-      </c>
-      <c r="C99" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D99" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E99" s="45">
-        <v>10.0</v>
-      </c>
-      <c r="F99" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="G99" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="H99" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="I99" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="J99" s="45">
-        <v>10.0</v>
-      </c>
-      <c r="K99" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="L99" s="20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="22" t="s">
-        <v>169</v>
-      </c>
-      <c r="B100" s="22" t="s">
-        <v>168</v>
-      </c>
-      <c r="C100" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D100" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E100" s="45">
-        <v>11.0</v>
-      </c>
-      <c r="F100" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="G100" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="H100" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="I100" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="J100" s="45">
-        <v>11.0</v>
-      </c>
-      <c r="K100" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="L100" s="20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="22" t="s">
-        <v>170</v>
-      </c>
-      <c r="B101" s="22" t="s">
-        <v>169</v>
-      </c>
-      <c r="C101" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D101" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E101" s="45">
-        <v>12.0</v>
-      </c>
-      <c r="F101" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="G101" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="H101" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="I101" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="J101" s="45">
-        <v>12.0</v>
-      </c>
-      <c r="K101" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="L101" s="20" t="s">
-        <v>26</v>
-      </c>
-    </row>
     <row r="102">
-      <c r="A102" s="22"/>
-      <c r="B102" s="22"/>
-      <c r="C102" s="22"/>
-      <c r="D102" s="22"/>
-      <c r="E102" s="45"/>
-      <c r="F102" s="22"/>
-      <c r="G102" s="22"/>
-      <c r="H102" s="22"/>
-      <c r="I102" s="22"/>
+      <c r="A102" s="24"/>
+      <c r="B102" s="24"/>
+      <c r="C102" s="24"/>
+      <c r="D102" s="24"/>
+      <c r="E102" s="50"/>
+      <c r="F102" s="24"/>
+      <c r="G102" s="24"/>
+      <c r="H102" s="24"/>
+      <c r="I102" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -32825,4 +32861,1019 @@
   </hyperlinks>
   <drawing r:id="rId199"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="6" max="6" width="22.0"/>
+    <col customWidth="1" min="12" max="12" width="11.13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" s="26" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="E2" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="F2" s="53" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="H2" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="I2" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="J2" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="K2" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="L2" s="28" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="D3" s="32">
+        <v>1.0</v>
+      </c>
+      <c r="E3" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="54" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="H3" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="I3" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="J3" s="32">
+        <v>9.0</v>
+      </c>
+      <c r="K3" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="L3" s="54" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="D4" s="32">
+        <v>1.0</v>
+      </c>
+      <c r="E4" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="54" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="H4" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="I4" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="J4" s="32">
+        <v>10.0</v>
+      </c>
+      <c r="K4" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="L4" s="54" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="D5" s="45">
+        <v>1.0</v>
+      </c>
+      <c r="E5" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="54" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="H5" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="I5" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="J5" s="32">
+        <v>11.0</v>
+      </c>
+      <c r="K5" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="L5" s="54" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" s="32">
+        <v>1.0</v>
+      </c>
+      <c r="E6" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="54" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="H6" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="I6" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="J6" s="44">
+        <v>10.0</v>
+      </c>
+      <c r="K6" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="L6" s="54" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="D7" s="32">
+        <v>1.0</v>
+      </c>
+      <c r="E7" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="54" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="H7" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="I7" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="J7" s="44">
+        <v>11.0</v>
+      </c>
+      <c r="K7" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="L7" s="54" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="D8" s="45">
+        <v>1.0</v>
+      </c>
+      <c r="E8" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="54" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="H8" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="I8" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="J8" s="44">
+        <v>12.0</v>
+      </c>
+      <c r="K8" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="L8" s="54" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="D9" s="32">
+        <v>1.0</v>
+      </c>
+      <c r="E9" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="54" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="H9" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="I9" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="J9" s="44">
+        <v>10.0</v>
+      </c>
+      <c r="K9" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L9" s="54" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="D10" s="32">
+        <v>1.0</v>
+      </c>
+      <c r="E10" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="54" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="H10" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="I10" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="J10" s="44">
+        <v>11.0</v>
+      </c>
+      <c r="K10" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L10" s="54" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="D11" s="45">
+        <v>1.0</v>
+      </c>
+      <c r="E11" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="F11" s="54" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="I11" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="J11" s="44">
+        <v>12.0</v>
+      </c>
+      <c r="K11" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="L11" s="54" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="D12" s="32">
+        <v>1.0</v>
+      </c>
+      <c r="E12" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="54" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="H12" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="I12" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="J12" s="44">
+        <v>10.0</v>
+      </c>
+      <c r="K12" s="44" t="s">
+        <v>38</v>
+      </c>
+      <c r="L12" s="54" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="D13" s="32">
+        <v>1.0</v>
+      </c>
+      <c r="E13" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="F13" s="54" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="H13" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="I13" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="J13" s="44">
+        <v>11.0</v>
+      </c>
+      <c r="K13" s="44" t="s">
+        <v>38</v>
+      </c>
+      <c r="L13" s="54" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="D14" s="45">
+        <v>1.0</v>
+      </c>
+      <c r="E14" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="54" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="H14" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="I14" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="J14" s="44">
+        <v>12.0</v>
+      </c>
+      <c r="K14" s="44" t="s">
+        <v>38</v>
+      </c>
+      <c r="L14" s="54" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="B15" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" s="39" t="s">
+        <v>130</v>
+      </c>
+      <c r="D15" s="46">
+        <v>1.0</v>
+      </c>
+      <c r="E15" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="F15" s="55">
+        <v>45967.0</v>
+      </c>
+      <c r="G15" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="H15" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="I15" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="J15" s="47">
+        <v>10.0</v>
+      </c>
+      <c r="K15" s="47" t="s">
+        <v>37</v>
+      </c>
+      <c r="L15" s="56">
+        <v>45967.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="B16" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" s="39" t="s">
+        <v>130</v>
+      </c>
+      <c r="D16" s="46">
+        <v>1.0</v>
+      </c>
+      <c r="E16" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="F16" s="55">
+        <v>45967.0</v>
+      </c>
+      <c r="G16" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="H16" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="I16" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="J16" s="47">
+        <v>11.0</v>
+      </c>
+      <c r="K16" s="47" t="s">
+        <v>37</v>
+      </c>
+      <c r="L16" s="56">
+        <v>45967.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="B17" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="39" t="s">
+        <v>130</v>
+      </c>
+      <c r="D17" s="46">
+        <v>1.0</v>
+      </c>
+      <c r="E17" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="F17" s="55">
+        <v>45967.0</v>
+      </c>
+      <c r="G17" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="H17" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="I17" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="J17" s="48">
+        <v>12.0</v>
+      </c>
+      <c r="K17" s="47" t="s">
+        <v>37</v>
+      </c>
+      <c r="L17" s="57">
+        <v>45967.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="24"/>
+      <c r="B18" s="34"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="50"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="24"/>
+      <c r="I18" s="34"/>
+      <c r="J18" s="50"/>
+      <c r="K18" s="21"/>
+      <c r="L18" s="51"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="24"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="50"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="24"/>
+      <c r="I19" s="34"/>
+      <c r="J19" s="50"/>
+      <c r="K19" s="21"/>
+      <c r="L19" s="51"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="24"/>
+      <c r="B20" s="34"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="50"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="34"/>
+      <c r="J20" s="50"/>
+      <c r="K20" s="24"/>
+      <c r="L20" s="52"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="24"/>
+      <c r="B21" s="34"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="50"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="34"/>
+      <c r="J21" s="50"/>
+      <c r="K21" s="21"/>
+      <c r="L21" s="51"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="24"/>
+      <c r="B22" s="34"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="50"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="50"/>
+      <c r="K22" s="21"/>
+      <c r="L22" s="51"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="24"/>
+      <c r="B23" s="34"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="50"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="34"/>
+      <c r="J23" s="50"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="52"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="24"/>
+      <c r="B24" s="34"/>
+      <c r="C24" s="34"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="24"/>
+      <c r="I24" s="34"/>
+      <c r="J24" s="50"/>
+      <c r="K24" s="21"/>
+      <c r="L24" s="51"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="24"/>
+      <c r="B25" s="34"/>
+      <c r="C25" s="34"/>
+      <c r="D25" s="50"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="24"/>
+      <c r="I25" s="34"/>
+      <c r="J25" s="50"/>
+      <c r="K25" s="21"/>
+      <c r="L25" s="51"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="24"/>
+      <c r="B26" s="34"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="50"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="24"/>
+      <c r="H26" s="24"/>
+      <c r="I26" s="34"/>
+      <c r="J26" s="50"/>
+      <c r="K26" s="24"/>
+      <c r="L26" s="52"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="24"/>
+      <c r="B27" s="34"/>
+      <c r="C27" s="34"/>
+      <c r="D27" s="50"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="24"/>
+      <c r="H27" s="24"/>
+      <c r="I27" s="34"/>
+      <c r="J27" s="50"/>
+      <c r="K27" s="24"/>
+      <c r="L27" s="51"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="50"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="24"/>
+      <c r="H28" s="24"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="50"/>
+      <c r="K28" s="21"/>
+      <c r="L28" s="51"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24"/>
+      <c r="B29" s="34"/>
+      <c r="C29" s="34"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="24"/>
+      <c r="H29" s="24"/>
+      <c r="I29" s="34"/>
+      <c r="J29" s="50"/>
+      <c r="K29" s="21"/>
+      <c r="L29" s="52"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24"/>
+      <c r="B30" s="34"/>
+      <c r="C30" s="34"/>
+      <c r="D30" s="50"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="24"/>
+      <c r="H30" s="24"/>
+      <c r="I30" s="34"/>
+      <c r="J30" s="50"/>
+      <c r="K30" s="21"/>
+      <c r="L30" s="21"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24"/>
+      <c r="B31" s="34"/>
+      <c r="C31" s="34"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="24"/>
+      <c r="H31" s="24"/>
+      <c r="I31" s="34"/>
+      <c r="J31" s="50"/>
+      <c r="K31" s="21"/>
+      <c r="L31" s="21"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24"/>
+      <c r="B32" s="34"/>
+      <c r="C32" s="34"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="24"/>
+      <c r="H32" s="24"/>
+      <c r="I32" s="34"/>
+      <c r="J32" s="50"/>
+      <c r="K32" s="24"/>
+      <c r="L32" s="24"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24"/>
+      <c r="B33" s="34"/>
+      <c r="C33" s="34"/>
+      <c r="D33" s="50"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="24"/>
+      <c r="H33" s="24"/>
+      <c r="I33" s="34"/>
+      <c r="J33" s="50"/>
+      <c r="K33" s="21"/>
+      <c r="L33" s="21"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24"/>
+      <c r="B34" s="34"/>
+      <c r="C34" s="34"/>
+      <c r="D34" s="50"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="24"/>
+      <c r="H34" s="24"/>
+      <c r="I34" s="34"/>
+      <c r="J34" s="50"/>
+      <c r="K34" s="21"/>
+      <c r="L34" s="21"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24"/>
+      <c r="B35" s="34"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="50"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="24"/>
+      <c r="H35" s="24"/>
+      <c r="I35" s="34"/>
+      <c r="J35" s="50"/>
+      <c r="K35" s="24"/>
+      <c r="L35" s="24"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="24"/>
+      <c r="B36" s="34"/>
+      <c r="C36" s="34"/>
+      <c r="D36" s="50"/>
+      <c r="E36" s="24"/>
+      <c r="F36" s="24"/>
+      <c r="G36" s="24"/>
+      <c r="H36" s="24"/>
+      <c r="I36" s="34"/>
+      <c r="J36" s="50"/>
+      <c r="K36" s="21"/>
+      <c r="L36" s="21"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="24"/>
+      <c r="B37" s="34"/>
+      <c r="C37" s="34"/>
+      <c r="D37" s="50"/>
+      <c r="E37" s="24"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="24"/>
+      <c r="H37" s="24"/>
+      <c r="I37" s="34"/>
+      <c r="J37" s="50"/>
+      <c r="K37" s="21"/>
+      <c r="L37" s="21"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="24"/>
+      <c r="B38" s="34"/>
+      <c r="C38" s="34"/>
+      <c r="D38" s="50"/>
+      <c r="E38" s="24"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="24"/>
+      <c r="H38" s="24"/>
+      <c r="I38" s="34"/>
+      <c r="J38" s="50"/>
+      <c r="K38" s="24"/>
+      <c r="L38" s="21"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="24"/>
+      <c r="B39" s="34"/>
+      <c r="C39" s="34"/>
+      <c r="D39" s="50"/>
+      <c r="E39" s="24"/>
+      <c r="F39" s="24"/>
+      <c r="G39" s="24"/>
+      <c r="H39" s="24"/>
+      <c r="I39" s="34"/>
+      <c r="J39" s="50"/>
+      <c r="K39" s="21"/>
+      <c r="L39" s="21"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="24"/>
+      <c r="B40" s="34"/>
+      <c r="C40" s="34"/>
+      <c r="D40" s="50"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="24"/>
+      <c r="H40" s="24"/>
+      <c r="I40" s="34"/>
+      <c r="J40" s="50"/>
+      <c r="K40" s="21"/>
+      <c r="L40" s="21"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="24"/>
+      <c r="B41" s="34"/>
+      <c r="C41" s="34"/>
+      <c r="D41" s="50"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="24"/>
+      <c r="H41" s="24"/>
+      <c r="I41" s="34"/>
+      <c r="J41" s="50"/>
+      <c r="K41" s="24"/>
+      <c r="L41" s="21"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="24"/>
+      <c r="B42" s="24"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="50"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="24"/>
+      <c r="H42" s="24"/>
+      <c r="I42" s="24"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="G1:L1"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="C3"/>
+    <hyperlink r:id="rId2" ref="I3"/>
+    <hyperlink r:id="rId3" ref="C4"/>
+    <hyperlink r:id="rId4" ref="I4"/>
+    <hyperlink r:id="rId5" ref="C5"/>
+    <hyperlink r:id="rId6" ref="I5"/>
+    <hyperlink r:id="rId7" ref="C6"/>
+    <hyperlink r:id="rId8" ref="I6"/>
+    <hyperlink r:id="rId9" ref="C7"/>
+    <hyperlink r:id="rId10" ref="I7"/>
+    <hyperlink r:id="rId11" ref="C8"/>
+    <hyperlink r:id="rId12" ref="I8"/>
+    <hyperlink r:id="rId13" ref="C9"/>
+    <hyperlink r:id="rId14" ref="I9"/>
+    <hyperlink r:id="rId15" ref="C10"/>
+    <hyperlink r:id="rId16" ref="I10"/>
+    <hyperlink r:id="rId17" ref="C11"/>
+    <hyperlink r:id="rId18" ref="I11"/>
+    <hyperlink r:id="rId19" ref="C12"/>
+    <hyperlink r:id="rId20" ref="I12"/>
+    <hyperlink r:id="rId21" ref="C13"/>
+    <hyperlink r:id="rId22" ref="I13"/>
+    <hyperlink r:id="rId23" ref="C14"/>
+    <hyperlink r:id="rId24" ref="I14"/>
+    <hyperlink r:id="rId25" ref="C15"/>
+    <hyperlink r:id="rId26" ref="I15"/>
+    <hyperlink r:id="rId27" ref="C16"/>
+    <hyperlink r:id="rId28" ref="I16"/>
+    <hyperlink r:id="rId29" ref="C17"/>
+    <hyperlink r:id="rId30" ref="I17"/>
+  </hyperlinks>
+  <drawing r:id="rId31"/>
+</worksheet>
 </file>
--- a/examples/example2/Example2.xlsx
+++ b/examples/example2/Example2.xlsx
@@ -13,14 +13,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataChecksum="4LWpCG6rA7Wf9jdQC/J2kTZGJkWgbD7X/U3cwDur9zs="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataChecksum="HMVqssnvImxjTBF/stQ501EaNePC35JgYuFZIzi9jMQ="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1279" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1249" uniqueCount="170">
   <si>
     <t>USUBJID</t>
   </si>
@@ -32870,8 +32870,16 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="6" max="6" width="22.0"/>
-    <col customWidth="1" min="12" max="12" width="11.13"/>
+    <col customWidth="1" min="1" max="1" width="10.0"/>
+    <col customWidth="1" min="2" max="2" width="8.13"/>
+    <col customWidth="1" min="4" max="4" width="8.38"/>
+    <col customWidth="1" min="5" max="5" width="11.38"/>
+    <col customWidth="1" min="6" max="6" width="21.0"/>
+    <col customWidth="1" min="7" max="7" width="9.88"/>
+    <col customWidth="1" min="8" max="8" width="7.25"/>
+    <col customWidth="1" min="10" max="10" width="7.75"/>
+    <col customWidth="1" min="11" max="11" width="11.25"/>
+    <col customWidth="1" min="12" max="12" width="21.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -32948,14 +32956,14 @@
       <c r="I3" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="J3" s="32">
-        <v>9.0</v>
-      </c>
-      <c r="K3" s="32" t="s">
-        <v>14</v>
+      <c r="J3" s="44">
+        <v>10.0</v>
+      </c>
+      <c r="K3" s="44" t="s">
+        <v>35</v>
       </c>
       <c r="L3" s="54" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
@@ -32986,14 +32994,14 @@
       <c r="I4" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="J4" s="32">
-        <v>10.0</v>
-      </c>
-      <c r="K4" s="32" t="s">
-        <v>14</v>
+      <c r="J4" s="44">
+        <v>11.0</v>
+      </c>
+      <c r="K4" s="44" t="s">
+        <v>35</v>
       </c>
       <c r="L4" s="54" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5">
@@ -33024,14 +33032,14 @@
       <c r="I5" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="J5" s="32">
-        <v>11.0</v>
-      </c>
-      <c r="K5" s="32" t="s">
-        <v>14</v>
+      <c r="J5" s="44">
+        <v>12.0</v>
+      </c>
+      <c r="K5" s="44" t="s">
+        <v>35</v>
       </c>
       <c r="L5" s="54" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6">
@@ -33066,10 +33074,10 @@
         <v>10.0</v>
       </c>
       <c r="K6" s="44" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L6" s="54" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
@@ -33104,10 +33112,10 @@
         <v>11.0</v>
       </c>
       <c r="K7" s="44" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L7" s="54" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
@@ -33142,10 +33150,10 @@
         <v>12.0</v>
       </c>
       <c r="K8" s="44" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L8" s="54" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9">
@@ -33180,10 +33188,10 @@
         <v>10.0</v>
       </c>
       <c r="K9" s="44" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L9" s="54" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10">
@@ -33218,10 +33226,10 @@
         <v>11.0</v>
       </c>
       <c r="K10" s="44" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L10" s="54" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11">
@@ -33256,239 +33264,167 @@
         <v>12.0</v>
       </c>
       <c r="K11" s="44" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L11" s="54" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="29" t="s">
+      <c r="A12" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="B12" s="30" t="s">
+      <c r="B12" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="C12" s="33" t="s">
+      <c r="C12" s="39" t="s">
         <v>130</v>
       </c>
-      <c r="D12" s="32">
+      <c r="D12" s="46">
         <v>1.0</v>
       </c>
-      <c r="E12" s="32" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" s="54" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="32" t="s">
+      <c r="E12" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="F12" s="55">
+        <v>45967.0</v>
+      </c>
+      <c r="G12" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="H12" s="32" t="s">
+      <c r="H12" s="37" t="s">
         <v>67</v>
       </c>
-      <c r="I12" s="33" t="s">
+      <c r="I12" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="J12" s="44">
+      <c r="J12" s="47">
         <v>10.0</v>
       </c>
-      <c r="K12" s="44" t="s">
-        <v>38</v>
-      </c>
-      <c r="L12" s="54" t="s">
-        <v>53</v>
+      <c r="K12" s="47" t="s">
+        <v>37</v>
+      </c>
+      <c r="L12" s="56">
+        <v>45967.0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="29" t="s">
+      <c r="A13" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="33" t="s">
+      <c r="C13" s="39" t="s">
         <v>130</v>
       </c>
-      <c r="D13" s="32">
+      <c r="D13" s="46">
         <v>1.0</v>
       </c>
-      <c r="E13" s="32" t="s">
-        <v>3</v>
-      </c>
-      <c r="F13" s="54" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="32" t="s">
+      <c r="E13" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="F13" s="55">
+        <v>45967.0</v>
+      </c>
+      <c r="G13" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="H13" s="32" t="s">
+      <c r="H13" s="37" t="s">
         <v>67</v>
       </c>
-      <c r="I13" s="33" t="s">
+      <c r="I13" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="J13" s="44">
+      <c r="J13" s="47">
         <v>11.0</v>
       </c>
-      <c r="K13" s="44" t="s">
-        <v>38</v>
-      </c>
-      <c r="L13" s="54" t="s">
-        <v>54</v>
+      <c r="K13" s="47" t="s">
+        <v>37</v>
+      </c>
+      <c r="L13" s="56">
+        <v>45967.0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="29" t="s">
+      <c r="A14" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="B14" s="30" t="s">
+      <c r="B14" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="33" t="s">
+      <c r="C14" s="39" t="s">
         <v>130</v>
       </c>
-      <c r="D14" s="45">
+      <c r="D14" s="46">
         <v>1.0</v>
       </c>
-      <c r="E14" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="54" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" s="29" t="s">
+      <c r="E14" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="F14" s="55">
+        <v>45967.0</v>
+      </c>
+      <c r="G14" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="H14" s="29" t="s">
+      <c r="H14" s="37" t="s">
         <v>67</v>
       </c>
-      <c r="I14" s="33" t="s">
+      <c r="I14" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="J14" s="44">
+      <c r="J14" s="48">
         <v>12.0</v>
       </c>
-      <c r="K14" s="44" t="s">
-        <v>38</v>
-      </c>
-      <c r="L14" s="54" t="s">
-        <v>55</v>
+      <c r="K14" s="47" t="s">
+        <v>37</v>
+      </c>
+      <c r="L14" s="57">
+        <v>45967.0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="B15" s="38" t="s">
-        <v>67</v>
-      </c>
-      <c r="C15" s="39" t="s">
-        <v>130</v>
-      </c>
-      <c r="D15" s="46">
-        <v>1.0</v>
-      </c>
-      <c r="E15" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="F15" s="55">
-        <v>45967.0</v>
-      </c>
-      <c r="G15" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="H15" s="37" t="s">
-        <v>67</v>
-      </c>
-      <c r="I15" s="39" t="s">
-        <v>69</v>
-      </c>
-      <c r="J15" s="47">
-        <v>10.0</v>
-      </c>
-      <c r="K15" s="47" t="s">
-        <v>37</v>
-      </c>
-      <c r="L15" s="56">
-        <v>45967.0</v>
-      </c>
+      <c r="A15" s="24"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="50"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="24"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="50"/>
+      <c r="K15" s="21"/>
+      <c r="L15" s="51"/>
     </row>
     <row r="16">
-      <c r="A16" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="B16" s="38" t="s">
-        <v>67</v>
-      </c>
-      <c r="C16" s="39" t="s">
-        <v>130</v>
-      </c>
-      <c r="D16" s="46">
-        <v>1.0</v>
-      </c>
-      <c r="E16" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="F16" s="55">
-        <v>45967.0</v>
-      </c>
-      <c r="G16" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="H16" s="37" t="s">
-        <v>67</v>
-      </c>
-      <c r="I16" s="39" t="s">
-        <v>69</v>
-      </c>
-      <c r="J16" s="47">
-        <v>11.0</v>
-      </c>
-      <c r="K16" s="47" t="s">
-        <v>37</v>
-      </c>
-      <c r="L16" s="56">
-        <v>45967.0</v>
-      </c>
+      <c r="A16" s="24"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="50"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="34"/>
+      <c r="J16" s="50"/>
+      <c r="K16" s="21"/>
+      <c r="L16" s="51"/>
     </row>
     <row r="17">
-      <c r="A17" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="B17" s="38" t="s">
-        <v>67</v>
-      </c>
-      <c r="C17" s="39" t="s">
-        <v>130</v>
-      </c>
-      <c r="D17" s="46">
-        <v>1.0</v>
-      </c>
-      <c r="E17" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="F17" s="55">
-        <v>45967.0</v>
-      </c>
-      <c r="G17" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="H17" s="37" t="s">
-        <v>67</v>
-      </c>
-      <c r="I17" s="39" t="s">
-        <v>69</v>
-      </c>
-      <c r="J17" s="48">
-        <v>12.0</v>
-      </c>
-      <c r="K17" s="47" t="s">
-        <v>37</v>
-      </c>
-      <c r="L17" s="57">
-        <v>45967.0</v>
-      </c>
+      <c r="A17" s="24"/>
+      <c r="B17" s="34"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="50"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="34"/>
+      <c r="J17" s="50"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="52"/>
     </row>
     <row r="18">
       <c r="A18" s="24"/>
@@ -33585,7 +33521,7 @@
       <c r="H24" s="24"/>
       <c r="I24" s="34"/>
       <c r="J24" s="50"/>
-      <c r="K24" s="21"/>
+      <c r="K24" s="24"/>
       <c r="L24" s="51"/>
     </row>
     <row r="25">
@@ -33613,7 +33549,7 @@
       <c r="H26" s="24"/>
       <c r="I26" s="34"/>
       <c r="J26" s="50"/>
-      <c r="K26" s="24"/>
+      <c r="K26" s="21"/>
       <c r="L26" s="52"/>
     </row>
     <row r="27">
@@ -33627,8 +33563,8 @@
       <c r="H27" s="24"/>
       <c r="I27" s="34"/>
       <c r="J27" s="50"/>
-      <c r="K27" s="24"/>
-      <c r="L27" s="51"/>
+      <c r="K27" s="21"/>
+      <c r="L27" s="21"/>
     </row>
     <row r="28">
       <c r="A28" s="24"/>
@@ -33642,7 +33578,7 @@
       <c r="I28" s="34"/>
       <c r="J28" s="50"/>
       <c r="K28" s="21"/>
-      <c r="L28" s="51"/>
+      <c r="L28" s="21"/>
     </row>
     <row r="29">
       <c r="A29" s="24"/>
@@ -33655,8 +33591,8 @@
       <c r="H29" s="24"/>
       <c r="I29" s="34"/>
       <c r="J29" s="50"/>
-      <c r="K29" s="21"/>
-      <c r="L29" s="52"/>
+      <c r="K29" s="24"/>
+      <c r="L29" s="24"/>
     </row>
     <row r="30">
       <c r="A30" s="24"/>
@@ -33740,7 +33676,7 @@
       <c r="I35" s="34"/>
       <c r="J35" s="50"/>
       <c r="K35" s="24"/>
-      <c r="L35" s="24"/>
+      <c r="L35" s="21"/>
     </row>
     <row r="36">
       <c r="A36" s="24"/>
@@ -33786,61 +33722,19 @@
     </row>
     <row r="39">
       <c r="A39" s="24"/>
-      <c r="B39" s="34"/>
-      <c r="C39" s="34"/>
+      <c r="B39" s="24"/>
+      <c r="C39" s="24"/>
       <c r="D39" s="50"/>
       <c r="E39" s="24"/>
       <c r="F39" s="24"/>
       <c r="G39" s="24"/>
       <c r="H39" s="24"/>
-      <c r="I39" s="34"/>
-      <c r="J39" s="50"/>
-      <c r="K39" s="21"/>
-      <c r="L39" s="21"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="24"/>
-      <c r="B40" s="34"/>
-      <c r="C40" s="34"/>
-      <c r="D40" s="50"/>
-      <c r="E40" s="24"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="24"/>
-      <c r="H40" s="24"/>
-      <c r="I40" s="34"/>
-      <c r="J40" s="50"/>
-      <c r="K40" s="21"/>
-      <c r="L40" s="21"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="24"/>
-      <c r="B41" s="34"/>
-      <c r="C41" s="34"/>
-      <c r="D41" s="50"/>
-      <c r="E41" s="24"/>
-      <c r="F41" s="24"/>
-      <c r="G41" s="24"/>
-      <c r="H41" s="24"/>
-      <c r="I41" s="34"/>
-      <c r="J41" s="50"/>
-      <c r="K41" s="24"/>
-      <c r="L41" s="21"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="24"/>
-      <c r="B42" s="24"/>
-      <c r="C42" s="24"/>
-      <c r="D42" s="50"/>
-      <c r="E42" s="24"/>
-      <c r="F42" s="24"/>
-      <c r="G42" s="24"/>
-      <c r="H42" s="24"/>
-      <c r="I42" s="24"/>
+      <c r="I39" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="G1:L1"/>
-    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="C3"/>
@@ -33867,13 +33761,7 @@
     <hyperlink r:id="rId22" ref="I13"/>
     <hyperlink r:id="rId23" ref="C14"/>
     <hyperlink r:id="rId24" ref="I14"/>
-    <hyperlink r:id="rId25" ref="C15"/>
-    <hyperlink r:id="rId26" ref="I15"/>
-    <hyperlink r:id="rId27" ref="C16"/>
-    <hyperlink r:id="rId28" ref="I16"/>
-    <hyperlink r:id="rId29" ref="C17"/>
-    <hyperlink r:id="rId30" ref="I17"/>
   </hyperlinks>
-  <drawing r:id="rId31"/>
+  <drawing r:id="rId25"/>
 </worksheet>
 </file>